--- a/research/traditional_assets/database/data/bermuda/bermuda_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_coal_related_energy.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="asx_ikw" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>1.641</v>
+        <v>2.66</v>
       </c>
       <c r="G2">
-        <v>0.05866666666666667</v>
+        <v>0.2359767891682785</v>
       </c>
       <c r="H2">
-        <v>0.05866666666666667</v>
+        <v>0.2359767891682785</v>
       </c>
       <c r="I2">
-        <v>-0.04274074074074074</v>
+        <v>0.1872340425531915</v>
       </c>
       <c r="J2">
-        <v>-0.04274074074074074</v>
+        <v>0.1872340425531915</v>
       </c>
       <c r="K2">
-        <v>-0.694</v>
+        <v>7.73</v>
       </c>
       <c r="L2">
-        <v>-0.0514074074074074</v>
+        <v>0.1495164410058027</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +626,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.16</v>
+        <v>1.27</v>
       </c>
       <c r="V2">
-        <v>0.008205128205128205</v>
+        <v>0.1016</v>
       </c>
       <c r="W2">
-        <v>-0.04420382165605095</v>
+        <v>0.408994708994709</v>
       </c>
       <c r="X2">
-        <v>0.07987334619781003</v>
+        <v>0.1416000868434379</v>
       </c>
       <c r="Y2">
-        <v>-0.124077167853861</v>
+        <v>0.2673946221512711</v>
       </c>
       <c r="Z2">
-        <v>0.9452457638986137</v>
+        <v>2.232297063903282</v>
       </c>
       <c r="AA2">
-        <v>-0.04040050413107408</v>
+        <v>0.4179620034542314</v>
       </c>
       <c r="AB2">
-        <v>0.08360720289782728</v>
+        <v>0.1396652613562268</v>
       </c>
       <c r="AC2">
-        <v>-0.1240077070289013</v>
+        <v>0.2782967420980046</v>
       </c>
       <c r="AD2">
-        <v>4.42</v>
+        <v>0.343</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.42</v>
+        <v>0.343</v>
       </c>
       <c r="AG2">
-        <v>4.26</v>
+        <v>-0.927</v>
       </c>
       <c r="AH2">
-        <v>0.1847826086956522</v>
+        <v>0.02670715564899167</v>
       </c>
       <c r="AI2">
-        <v>0.2082940622054666</v>
+        <v>0.01327245288859653</v>
       </c>
       <c r="AJ2">
-        <v>0.1792929292929293</v>
+        <v>-0.08010023330165039</v>
       </c>
       <c r="AK2">
-        <v>0.2022792022792022</v>
+        <v>-0.03772433158344524</v>
       </c>
       <c r="AL2">
-        <v>0.09</v>
+        <v>0.158</v>
       </c>
       <c r="AM2">
-        <v>0.08399999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="AN2">
-        <v>5.58080808080808</v>
+        <v>0.02811475409836066</v>
       </c>
       <c r="AO2">
-        <v>-6.411111111111111</v>
+        <v>61.26582278481013</v>
       </c>
       <c r="AP2">
-        <v>5.378787878787878</v>
+        <v>-0.07598360655737706</v>
       </c>
       <c r="AQ2">
-        <v>-6.86904761904762</v>
+        <v>93.98058252427184</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>1.641</v>
+        <v>2.66</v>
       </c>
       <c r="G3">
-        <v>0.05866666666666667</v>
+        <v>0.2359767891682785</v>
       </c>
       <c r="H3">
-        <v>0.05866666666666667</v>
+        <v>0.2359767891682785</v>
       </c>
       <c r="I3">
-        <v>-0.04274074074074074</v>
+        <v>0.1872340425531915</v>
       </c>
       <c r="J3">
-        <v>-0.04274074074074074</v>
+        <v>0.1872340425531915</v>
       </c>
       <c r="K3">
-        <v>-0.694</v>
+        <v>7.73</v>
       </c>
       <c r="L3">
-        <v>-0.0514074074074074</v>
+        <v>0.1495164410058027</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +754,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
+        <v>1.27</v>
+      </c>
+      <c r="V3">
+        <v>0.1016</v>
+      </c>
+      <c r="W3">
+        <v>0.408994708994709</v>
+      </c>
+      <c r="X3">
+        <v>0.1416000868434379</v>
+      </c>
+      <c r="Y3">
+        <v>0.2673946221512711</v>
+      </c>
+      <c r="Z3">
+        <v>2.232297063903282</v>
+      </c>
+      <c r="AA3">
+        <v>0.4179620034542314</v>
+      </c>
+      <c r="AB3">
+        <v>0.1396652613562268</v>
+      </c>
+      <c r="AC3">
+        <v>0.2782967420980046</v>
+      </c>
+      <c r="AD3">
+        <v>0.343</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0.343</v>
+      </c>
+      <c r="AG3">
+        <v>-0.927</v>
+      </c>
+      <c r="AH3">
+        <v>0.02670715564899167</v>
+      </c>
+      <c r="AI3">
+        <v>0.01327245288859653</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.08010023330165039</v>
+      </c>
+      <c r="AK3">
+        <v>-0.03772433158344524</v>
+      </c>
+      <c r="AL3">
+        <v>0.158</v>
+      </c>
+      <c r="AM3">
+        <v>0.103</v>
+      </c>
+      <c r="AN3">
+        <v>0.02811475409836066</v>
+      </c>
+      <c r="AO3">
+        <v>61.26582278481013</v>
+      </c>
+      <c r="AP3">
+        <v>-0.07598360655737706</v>
+      </c>
+      <c r="AQ3">
+        <v>93.98058252427184</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ikwezi Mining Limited (ASX:IKW)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ASX:IKW</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Coal &amp; Related Energy</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0267071556489917</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>12.5</v>
+      </c>
+      <c r="H2">
+        <v>12.8619798709856</v>
+      </c>
+      <c r="I2">
+        <v>11.573</v>
+      </c>
+      <c r="J2">
+        <v>11.5919798709856</v>
+      </c>
+      <c r="K2">
+        <v>0.343</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0.139665261356227</v>
+      </c>
+      <c r="N2">
+        <v>0.13885458892338</v>
+      </c>
+      <c r="O2">
+        <v>0.069154128440367</v>
+      </c>
+      <c r="P2">
+        <v>0.0457</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.141600086843438</v>
+      </c>
+      <c r="T2">
+        <v>0.13885458892338</v>
+      </c>
+      <c r="U2">
+        <v>1.3939336667829</v>
+      </c>
+      <c r="V2">
+        <v>1.35670566337976</v>
+      </c>
+      <c r="W2">
+        <v>10000000</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>12.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.07374819139040771</v>
+      </c>
+      <c r="AC2">
+        <v>0.06915412844036697</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>12.2</v>
+      </c>
+      <c r="AH2">
+        <v>0.08</v>
+      </c>
+      <c r="AI2">
+        <v>3.31</v>
+      </c>
+      <c r="AJ2">
+        <v>0.343</v>
+      </c>
+      <c r="AK2">
+        <v>0.343</v>
+      </c>
+      <c r="AL2">
+        <v>0.158</v>
+      </c>
+      <c r="AM2">
+        <v>0.343</v>
+      </c>
+      <c r="AN2">
+        <v>1.27</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1388545889233804</v>
+      </c>
+      <c r="C2">
+        <v>12.86197987098559</v>
+      </c>
+      <c r="D2">
+        <v>11.5919798709856</v>
+      </c>
+      <c r="E2">
+        <v>-0.343</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.27</v>
+      </c>
+      <c r="H2">
+        <v>12.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>12.2</v>
+      </c>
+      <c r="K2">
+        <v>0.08</v>
+      </c>
+      <c r="L2">
+        <v>12.12</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>12.12</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>12.12</v>
+      </c>
+      <c r="Q2">
+        <v>12.2</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1388545889233804</v>
+      </c>
+      <c r="T2">
+        <v>1.356705663379757</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0.0457</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1389235889233804</v>
+      </c>
+      <c r="C3">
+        <v>12.73193198471898</v>
+      </c>
+      <c r="D3">
+        <v>11.59036198471898</v>
+      </c>
+      <c r="E3">
+        <v>-0.21457</v>
+      </c>
+      <c r="F3">
+        <v>0.12843</v>
+      </c>
+      <c r="G3">
+        <v>1.27</v>
+      </c>
+      <c r="H3">
+        <v>12.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>12.2</v>
+      </c>
+      <c r="K3">
+        <v>0.08</v>
+      </c>
+      <c r="L3">
+        <v>12.12</v>
+      </c>
+      <c r="M3">
+        <v>0.005869251</v>
+      </c>
+      <c r="N3">
+        <v>12.114130749</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>12.114130749</v>
+      </c>
+      <c r="Q3">
+        <v>12.194130749</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1398652413367479</v>
+      </c>
+      <c r="T3">
+        <v>1.370409760989654</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0.0457</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>2064.999435191986</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1389925889233804</v>
+      </c>
+      <c r="C4">
+        <v>12.60188455000434</v>
+      </c>
+      <c r="D4">
+        <v>11.58874455000434</v>
+      </c>
+      <c r="E4">
+        <v>-0.08614000000000005</v>
+      </c>
+      <c r="F4">
+        <v>0.25686</v>
+      </c>
+      <c r="G4">
+        <v>1.27</v>
+      </c>
+      <c r="H4">
+        <v>12.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>12.2</v>
+      </c>
+      <c r="K4">
+        <v>0.08</v>
+      </c>
+      <c r="L4">
+        <v>12.12</v>
+      </c>
+      <c r="M4">
+        <v>0.011738502</v>
+      </c>
+      <c r="N4">
+        <v>12.108261498</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>12.108261498</v>
+      </c>
+      <c r="Q4">
+        <v>12.188261498</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1408965193095718</v>
+      </c>
+      <c r="T4">
+        <v>1.384393534060977</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0.0457</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>1032.499717595993</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1390615889233804</v>
+      </c>
+      <c r="C5">
+        <v>12.47183756665265</v>
+      </c>
+      <c r="D5">
+        <v>11.58712756665265</v>
+      </c>
+      <c r="E5">
+        <v>0.04228999999999994</v>
+      </c>
+      <c r="F5">
+        <v>0.38529</v>
+      </c>
+      <c r="G5">
+        <v>1.27</v>
+      </c>
+      <c r="H5">
+        <v>12.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>12.2</v>
+      </c>
+      <c r="K5">
+        <v>0.08</v>
+      </c>
+      <c r="L5">
+        <v>12.12</v>
+      </c>
+      <c r="M5">
+        <v>0.017607753</v>
+      </c>
+      <c r="N5">
+        <v>12.102392247</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>12.102392247</v>
+      </c>
+      <c r="Q5">
+        <v>12.182392247</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1419490607457529</v>
+      </c>
+      <c r="T5">
+        <v>1.398665632350265</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0.0457</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>688.3331450639953</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1391305889233804</v>
+      </c>
+      <c r="C6">
+        <v>12.34179103447502</v>
+      </c>
+      <c r="D6">
+        <v>11.58551103447502</v>
+      </c>
+      <c r="E6">
+        <v>0.1707199999999999</v>
+      </c>
+      <c r="F6">
+        <v>0.51372</v>
+      </c>
+      <c r="G6">
+        <v>1.27</v>
+      </c>
+      <c r="H6">
+        <v>12.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>12.2</v>
+      </c>
+      <c r="K6">
+        <v>0.08</v>
+      </c>
+      <c r="L6">
+        <v>12.12</v>
+      </c>
+      <c r="M6">
+        <v>0.023477004</v>
+      </c>
+      <c r="N6">
+        <v>12.096522996</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>12.096522996</v>
+      </c>
+      <c r="Q6">
+        <v>12.176522996</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1430235301285212</v>
+      </c>
+      <c r="T6">
+        <v>1.41323506602058</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0.0457</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>516.2498587979965</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1391995889233804</v>
+      </c>
+      <c r="C7">
+        <v>12.21174495328262</v>
+      </c>
+      <c r="D7">
+        <v>11.58389495328262</v>
+      </c>
+      <c r="E7">
+        <v>0.29915</v>
+      </c>
+      <c r="F7">
+        <v>0.64215</v>
+      </c>
+      <c r="G7">
+        <v>1.27</v>
+      </c>
+      <c r="H7">
+        <v>12.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>12.2</v>
+      </c>
+      <c r="K7">
+        <v>0.08</v>
+      </c>
+      <c r="L7">
+        <v>12.12</v>
+      </c>
+      <c r="M7">
+        <v>0.029346255</v>
+      </c>
+      <c r="N7">
+        <v>12.090653745</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>12.090653745</v>
+      </c>
+      <c r="Q7">
+        <v>12.170653745</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1441206199193477</v>
+      </c>
+      <c r="T7">
+        <v>1.42811122461027</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0.0457</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>412.9998870383972</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1392685889233804</v>
+      </c>
+      <c r="C8">
+        <v>12.08169932288676</v>
+      </c>
+      <c r="D8">
+        <v>11.58227932288676</v>
+      </c>
+      <c r="E8">
+        <v>0.4275799999999999</v>
+      </c>
+      <c r="F8">
+        <v>0.7705799999999999</v>
+      </c>
+      <c r="G8">
+        <v>1.27</v>
+      </c>
+      <c r="H8">
+        <v>12.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>12.2</v>
+      </c>
+      <c r="K8">
+        <v>0.08</v>
+      </c>
+      <c r="L8">
+        <v>12.12</v>
+      </c>
+      <c r="M8">
+        <v>0.035215506</v>
+      </c>
+      <c r="N8">
+        <v>12.084784494</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>12.084784494</v>
+      </c>
+      <c r="Q8">
+        <v>12.164784494</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1452410520461493</v>
+      </c>
+      <c r="T8">
+        <v>1.443303897212507</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0.0457</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>344.1665725319976</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1393375889233804</v>
+      </c>
+      <c r="C9">
+        <v>11.95165414309886</v>
+      </c>
+      <c r="D9">
+        <v>11.58066414309886</v>
+      </c>
+      <c r="E9">
+        <v>0.5560100000000001</v>
+      </c>
+      <c r="F9">
+        <v>0.8990100000000001</v>
+      </c>
+      <c r="G9">
+        <v>1.27</v>
+      </c>
+      <c r="H9">
+        <v>12.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>12.2</v>
+      </c>
+      <c r="K9">
+        <v>0.08</v>
+      </c>
+      <c r="L9">
+        <v>12.12</v>
+      </c>
+      <c r="M9">
+        <v>0.04108475700000001</v>
+      </c>
+      <c r="N9">
+        <v>12.078915243</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>12.078915243</v>
+      </c>
+      <c r="Q9">
+        <v>12.158915243</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1463855794875058</v>
+      </c>
+      <c r="T9">
+        <v>1.458823293956728</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0.0457</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>294.9999193131408</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1394065889233804</v>
+      </c>
+      <c r="C10">
+        <v>11.82160941373041</v>
+      </c>
+      <c r="D10">
+        <v>11.57904941373041</v>
+      </c>
+      <c r="E10">
+        <v>0.6844399999999999</v>
+      </c>
+      <c r="F10">
+        <v>1.02744</v>
+      </c>
+      <c r="G10">
+        <v>1.27</v>
+      </c>
+      <c r="H10">
+        <v>12.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>12.2</v>
+      </c>
+      <c r="K10">
+        <v>0.08</v>
+      </c>
+      <c r="L10">
+        <v>12.12</v>
+      </c>
+      <c r="M10">
+        <v>0.046954008</v>
+      </c>
+      <c r="N10">
+        <v>12.073045992</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>12.073045992</v>
+      </c>
+      <c r="Q10">
+        <v>12.153045992</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1475549879601961</v>
+      </c>
+      <c r="T10">
+        <v>1.47468006889104</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0.0457</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>258.1249293989982</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1394755889233804</v>
+      </c>
+      <c r="C11">
+        <v>11.69156513459304</v>
+      </c>
+      <c r="D11">
+        <v>11.57743513459304</v>
+      </c>
+      <c r="E11">
+        <v>0.81287</v>
+      </c>
+      <c r="F11">
+        <v>1.15587</v>
+      </c>
+      <c r="G11">
+        <v>1.27</v>
+      </c>
+      <c r="H11">
+        <v>12.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>12.2</v>
+      </c>
+      <c r="K11">
+        <v>0.08</v>
+      </c>
+      <c r="L11">
+        <v>12.12</v>
+      </c>
+      <c r="M11">
+        <v>0.052823259</v>
+      </c>
+      <c r="N11">
+        <v>12.067176741</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>12.067176741</v>
+      </c>
+      <c r="Q11">
+        <v>12.147176741</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1487500977180004</v>
+      </c>
+      <c r="T11">
+        <v>1.490885344373359</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0.0457</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>229.4443816879984</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1395445889233804</v>
+      </c>
+      <c r="C12">
+        <v>11.56152130549846</v>
+      </c>
+      <c r="D12">
+        <v>11.57582130549847</v>
+      </c>
+      <c r="E12">
+        <v>0.9413</v>
+      </c>
+      <c r="F12">
+        <v>1.2843</v>
+      </c>
+      <c r="G12">
+        <v>1.27</v>
+      </c>
+      <c r="H12">
+        <v>12.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>12.2</v>
+      </c>
+      <c r="K12">
+        <v>0.08</v>
+      </c>
+      <c r="L12">
+        <v>12.12</v>
+      </c>
+      <c r="M12">
+        <v>0.05869251</v>
+      </c>
+      <c r="N12">
+        <v>12.06130749</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>12.06130749</v>
+      </c>
+      <c r="Q12">
+        <v>12.14130749</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1499717654704227</v>
+      </c>
+      <c r="T12">
+        <v>1.507450737088619</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0.0457</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>206.4999435191986</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1396135889233804</v>
+      </c>
+      <c r="C13">
+        <v>11.43147792625851</v>
+      </c>
+      <c r="D13">
+        <v>11.57420792625851</v>
+      </c>
+      <c r="E13">
+        <v>1.06973</v>
+      </c>
+      <c r="F13">
+        <v>1.41273</v>
+      </c>
+      <c r="G13">
+        <v>1.27</v>
+      </c>
+      <c r="H13">
+        <v>12.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>12.2</v>
+      </c>
+      <c r="K13">
+        <v>0.08</v>
+      </c>
+      <c r="L13">
+        <v>12.12</v>
+      </c>
+      <c r="M13">
+        <v>0.06456176100000001</v>
+      </c>
+      <c r="N13">
+        <v>12.055438239</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>12.055438239</v>
+      </c>
+      <c r="Q13">
+        <v>12.135438239</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1512208864307645</v>
+      </c>
+      <c r="T13">
+        <v>1.524388385819952</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0.0457</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>187.7272213810896</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1396825889233804</v>
+      </c>
+      <c r="C14">
+        <v>11.30143499668511</v>
+      </c>
+      <c r="D14">
+        <v>11.57259499668511</v>
+      </c>
+      <c r="E14">
+        <v>1.19816</v>
+      </c>
+      <c r="F14">
+        <v>1.54116</v>
+      </c>
+      <c r="G14">
+        <v>1.27</v>
+      </c>
+      <c r="H14">
+        <v>12.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>12.2</v>
+      </c>
+      <c r="K14">
+        <v>0.08</v>
+      </c>
+      <c r="L14">
+        <v>12.12</v>
+      </c>
+      <c r="M14">
+        <v>0.070431012</v>
+      </c>
+      <c r="N14">
+        <v>12.049568988</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>12.049568988</v>
+      </c>
+      <c r="Q14">
+        <v>12.129568988</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1524983965038413</v>
+      </c>
+      <c r="T14">
+        <v>1.54171098111336</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0.0457</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>172.0832862659988</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1397515889233804</v>
+      </c>
+      <c r="C15">
+        <v>11.1713925165903</v>
+      </c>
+      <c r="D15">
+        <v>11.5709825165903</v>
+      </c>
+      <c r="E15">
+        <v>1.32659</v>
+      </c>
+      <c r="F15">
+        <v>1.66959</v>
+      </c>
+      <c r="G15">
+        <v>1.27</v>
+      </c>
+      <c r="H15">
+        <v>12.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>12.2</v>
+      </c>
+      <c r="K15">
+        <v>0.08</v>
+      </c>
+      <c r="L15">
+        <v>12.12</v>
+      </c>
+      <c r="M15">
+        <v>0.07630026300000001</v>
+      </c>
+      <c r="N15">
+        <v>12.043699737</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>12.043699737</v>
+      </c>
+      <c r="Q15">
+        <v>12.123699737</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1538052746245751</v>
+      </c>
+      <c r="T15">
+        <v>1.559431796988226</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0.0457</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>158.8461103993835</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1398205889233804</v>
+      </c>
+      <c r="C16">
+        <v>11.04135048578621</v>
+      </c>
+      <c r="D16">
+        <v>11.56937048578621</v>
+      </c>
+      <c r="E16">
+        <v>1.45502</v>
+      </c>
+      <c r="F16">
+        <v>1.79802</v>
+      </c>
+      <c r="G16">
+        <v>1.27</v>
+      </c>
+      <c r="H16">
+        <v>12.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>12.2</v>
+      </c>
+      <c r="K16">
+        <v>0.08</v>
+      </c>
+      <c r="L16">
+        <v>12.12</v>
+      </c>
+      <c r="M16">
+        <v>0.08216951400000001</v>
+      </c>
+      <c r="N16">
+        <v>12.037830486</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>12.037830486</v>
+      </c>
+      <c r="Q16">
+        <v>12.117830486</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1551425452597446</v>
+      </c>
+      <c r="T16">
+        <v>1.577564724860183</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0.0457</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>147.4999596565704</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1398895889233804</v>
+      </c>
+      <c r="C17">
+        <v>10.9113089040851</v>
+      </c>
+      <c r="D17">
+        <v>11.5677589040851</v>
+      </c>
+      <c r="E17">
+        <v>1.58345</v>
+      </c>
+      <c r="F17">
+        <v>1.92645</v>
+      </c>
+      <c r="G17">
+        <v>1.27</v>
+      </c>
+      <c r="H17">
+        <v>12.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>12.2</v>
+      </c>
+      <c r="K17">
+        <v>0.08</v>
+      </c>
+      <c r="L17">
+        <v>12.12</v>
+      </c>
+      <c r="M17">
+        <v>0.088038765</v>
+      </c>
+      <c r="N17">
+        <v>12.031961235</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>12.031961235</v>
+      </c>
+      <c r="Q17">
+        <v>12.111961235</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1565112810863298</v>
+      </c>
+      <c r="T17">
+        <v>1.596124309858538</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0.0457</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>137.6666290127991</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
         <v>0.16</v>
       </c>
-      <c r="V3">
-        <v>0.008205128205128205</v>
-      </c>
-      <c r="W3">
-        <v>-0.04420382165605095</v>
-      </c>
-      <c r="X3">
-        <v>0.07987334619781003</v>
-      </c>
-      <c r="Y3">
-        <v>-0.124077167853861</v>
-      </c>
-      <c r="Z3">
-        <v>0.9452457638986137</v>
-      </c>
-      <c r="AA3">
-        <v>-0.04040050413107408</v>
-      </c>
-      <c r="AB3">
-        <v>0.08360720289782728</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1240077070289013</v>
-      </c>
-      <c r="AD3">
-        <v>4.42</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>4.42</v>
-      </c>
-      <c r="AG3">
-        <v>4.26</v>
-      </c>
-      <c r="AH3">
-        <v>0.1847826086956522</v>
-      </c>
-      <c r="AI3">
-        <v>0.2082940622054666</v>
-      </c>
-      <c r="AJ3">
-        <v>0.1792929292929293</v>
-      </c>
-      <c r="AK3">
-        <v>0.2022792022792022</v>
-      </c>
-      <c r="AL3">
-        <v>0.09</v>
-      </c>
-      <c r="AM3">
-        <v>0.08399999999999999</v>
-      </c>
-      <c r="AN3">
-        <v>5.58080808080808</v>
-      </c>
-      <c r="AO3">
-        <v>-6.411111111111111</v>
-      </c>
-      <c r="AP3">
-        <v>5.378787878787878</v>
-      </c>
-      <c r="AQ3">
-        <v>-6.86904761904762</v>
+      <c r="B18">
+        <v>0.1399585889233804</v>
+      </c>
+      <c r="C18">
+        <v>10.78126777129932</v>
+      </c>
+      <c r="D18">
+        <v>11.56614777129932</v>
+      </c>
+      <c r="E18">
+        <v>1.71188</v>
+      </c>
+      <c r="F18">
+        <v>2.05488</v>
+      </c>
+      <c r="G18">
+        <v>1.27</v>
+      </c>
+      <c r="H18">
+        <v>12.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>12.2</v>
+      </c>
+      <c r="K18">
+        <v>0.08</v>
+      </c>
+      <c r="L18">
+        <v>12.12</v>
+      </c>
+      <c r="M18">
+        <v>0.093908016</v>
+      </c>
+      <c r="N18">
+        <v>12.026091984</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>12.026091984</v>
+      </c>
+      <c r="Q18">
+        <v>12.106091984</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1579126058611671</v>
+      </c>
+      <c r="T18">
+        <v>1.615125789737806</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0.0457</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>129.0624646994991</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1400275889233804</v>
+      </c>
+      <c r="C19">
+        <v>10.6512270872413</v>
+      </c>
+      <c r="D19">
+        <v>11.56453708724131</v>
+      </c>
+      <c r="E19">
+        <v>1.84031</v>
+      </c>
+      <c r="F19">
+        <v>2.18331</v>
+      </c>
+      <c r="G19">
+        <v>1.27</v>
+      </c>
+      <c r="H19">
+        <v>12.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>12.2</v>
+      </c>
+      <c r="K19">
+        <v>0.08</v>
+      </c>
+      <c r="L19">
+        <v>12.12</v>
+      </c>
+      <c r="M19">
+        <v>0.09977726700000002</v>
+      </c>
+      <c r="N19">
+        <v>12.020222733</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>12.020222733</v>
+      </c>
+      <c r="Q19">
+        <v>12.100222733</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1593476974980487</v>
+      </c>
+      <c r="T19">
+        <v>1.634585136602117</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0.0457</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>121.4705550112933</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1400965889233804</v>
+      </c>
+      <c r="C20">
+        <v>10.52118685172363</v>
+      </c>
+      <c r="D20">
+        <v>11.56292685172363</v>
+      </c>
+      <c r="E20">
+        <v>1.96874</v>
+      </c>
+      <c r="F20">
+        <v>2.31174</v>
+      </c>
+      <c r="G20">
+        <v>1.27</v>
+      </c>
+      <c r="H20">
+        <v>12.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>12.2</v>
+      </c>
+      <c r="K20">
+        <v>0.08</v>
+      </c>
+      <c r="L20">
+        <v>12.12</v>
+      </c>
+      <c r="M20">
+        <v>0.105646518</v>
+      </c>
+      <c r="N20">
+        <v>12.014353482</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>12.014353482</v>
+      </c>
+      <c r="Q20">
+        <v>12.094353482</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1608177913699761</v>
+      </c>
+      <c r="T20">
+        <v>1.65451910168263</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0.0457</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>114.7221908439992</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1401655889233804</v>
+      </c>
+      <c r="C21">
+        <v>10.39114706455896</v>
+      </c>
+      <c r="D21">
+        <v>11.56131706455896</v>
+      </c>
+      <c r="E21">
+        <v>2.09717</v>
+      </c>
+      <c r="F21">
+        <v>2.44017</v>
+      </c>
+      <c r="G21">
+        <v>1.27</v>
+      </c>
+      <c r="H21">
+        <v>12.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>12.2</v>
+      </c>
+      <c r="K21">
+        <v>0.08</v>
+      </c>
+      <c r="L21">
+        <v>12.12</v>
+      </c>
+      <c r="M21">
+        <v>0.111515769</v>
+      </c>
+      <c r="N21">
+        <v>12.008484231</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>12.008484231</v>
+      </c>
+      <c r="Q21">
+        <v>12.088484231</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1623241838560252</v>
+      </c>
+      <c r="T21">
+        <v>1.674945263431799</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0.0457</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>108.6841807995782</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1402345889233804</v>
+      </c>
+      <c r="C22">
+        <v>10.26110772556005</v>
+      </c>
+      <c r="D22">
+        <v>11.55970772556005</v>
+      </c>
+      <c r="E22">
+        <v>2.2256</v>
+      </c>
+      <c r="F22">
+        <v>2.5686</v>
+      </c>
+      <c r="G22">
+        <v>1.27</v>
+      </c>
+      <c r="H22">
+        <v>12.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>12.2</v>
+      </c>
+      <c r="K22">
+        <v>0.08</v>
+      </c>
+      <c r="L22">
+        <v>12.12</v>
+      </c>
+      <c r="M22">
+        <v>0.11738502</v>
+      </c>
+      <c r="N22">
+        <v>12.00261498</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>12.00261498</v>
+      </c>
+      <c r="Q22">
+        <v>12.08261498</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1638682361542255</v>
+      </c>
+      <c r="T22">
+        <v>1.695882079224696</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0.0457</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>103.2499717595993</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1403035889233804</v>
+      </c>
+      <c r="C23">
+        <v>10.13106883453979</v>
+      </c>
+      <c r="D23">
+        <v>11.55809883453979</v>
+      </c>
+      <c r="E23">
+        <v>2.35403</v>
+      </c>
+      <c r="F23">
+        <v>2.69703</v>
+      </c>
+      <c r="G23">
+        <v>1.27</v>
+      </c>
+      <c r="H23">
+        <v>12.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>12.2</v>
+      </c>
+      <c r="K23">
+        <v>0.08</v>
+      </c>
+      <c r="L23">
+        <v>12.12</v>
+      </c>
+      <c r="M23">
+        <v>0.123254271</v>
+      </c>
+      <c r="N23">
+        <v>11.996745729</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>11.996745729</v>
+      </c>
+      <c r="Q23">
+        <v>12.076745729</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1654513783840258</v>
+      </c>
+      <c r="T23">
+        <v>1.717348940987034</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0.0457</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>98.33330643771362</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1403725889233804</v>
+      </c>
+      <c r="C24">
+        <v>10.00103039131113</v>
+      </c>
+      <c r="D24">
+        <v>11.55649039131113</v>
+      </c>
+      <c r="E24">
+        <v>2.48246</v>
+      </c>
+      <c r="F24">
+        <v>2.82546</v>
+      </c>
+      <c r="G24">
+        <v>1.27</v>
+      </c>
+      <c r="H24">
+        <v>12.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>12.2</v>
+      </c>
+      <c r="K24">
+        <v>0.08</v>
+      </c>
+      <c r="L24">
+        <v>12.12</v>
+      </c>
+      <c r="M24">
+        <v>0.129123522</v>
+      </c>
+      <c r="N24">
+        <v>11.990876478</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>11.990876478</v>
+      </c>
+      <c r="Q24">
+        <v>12.070876478</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1670751140043338</v>
+      </c>
+      <c r="T24">
+        <v>1.739366235102252</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0.0457</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>93.8636106905448</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1404415889233804</v>
+      </c>
+      <c r="C25">
+        <v>9.870992395687175</v>
+      </c>
+      <c r="D25">
+        <v>11.55488239568717</v>
+      </c>
+      <c r="E25">
+        <v>2.61089</v>
+      </c>
+      <c r="F25">
+        <v>2.95389</v>
+      </c>
+      <c r="G25">
+        <v>1.27</v>
+      </c>
+      <c r="H25">
+        <v>12.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>12.2</v>
+      </c>
+      <c r="K25">
+        <v>0.08</v>
+      </c>
+      <c r="L25">
+        <v>12.12</v>
+      </c>
+      <c r="M25">
+        <v>0.134992773</v>
+      </c>
+      <c r="N25">
+        <v>11.985007227</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>11.985007227</v>
+      </c>
+      <c r="Q25">
+        <v>12.065007227</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1687410245758187</v>
+      </c>
+      <c r="T25">
+        <v>1.761955406986697</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0.0457</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>89.78258413878198</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1405105889233804</v>
+      </c>
+      <c r="C26">
+        <v>9.740954847481094</v>
+      </c>
+      <c r="D26">
+        <v>11.55327484748109</v>
+      </c>
+      <c r="E26">
+        <v>2.73932</v>
+      </c>
+      <c r="F26">
+        <v>3.08232</v>
+      </c>
+      <c r="G26">
+        <v>1.27</v>
+      </c>
+      <c r="H26">
+        <v>12.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>12.2</v>
+      </c>
+      <c r="K26">
+        <v>0.08</v>
+      </c>
+      <c r="L26">
+        <v>12.12</v>
+      </c>
+      <c r="M26">
+        <v>0.140862024</v>
+      </c>
+      <c r="N26">
+        <v>11.979137976</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>11.979137976</v>
+      </c>
+      <c r="Q26">
+        <v>12.059137976</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1704507748991847</v>
+      </c>
+      <c r="T26">
+        <v>1.785139030762838</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0.0457</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>86.04164313299941</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1405795889233803</v>
+      </c>
+      <c r="C27">
+        <v>9.610917746506178</v>
+      </c>
+      <c r="D27">
+        <v>11.55166774650618</v>
+      </c>
+      <c r="E27">
+        <v>2.86775</v>
+      </c>
+      <c r="F27">
+        <v>3.21075</v>
+      </c>
+      <c r="G27">
+        <v>1.27</v>
+      </c>
+      <c r="H27">
+        <v>12.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>12.2</v>
+      </c>
+      <c r="K27">
+        <v>0.08</v>
+      </c>
+      <c r="L27">
+        <v>12.12</v>
+      </c>
+      <c r="M27">
+        <v>0.146731275</v>
+      </c>
+      <c r="N27">
+        <v>11.973268725</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>11.973268725</v>
+      </c>
+      <c r="Q27">
+        <v>12.053268725</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1722061185645072</v>
+      </c>
+      <c r="T27">
+        <v>1.808940884506343</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0.0457</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>82.59997740767943</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1406485889233804</v>
+      </c>
+      <c r="C28">
+        <v>9.480881092575817</v>
+      </c>
+      <c r="D28">
+        <v>11.55006109257582</v>
+      </c>
+      <c r="E28">
+        <v>2.99618</v>
+      </c>
+      <c r="F28">
+        <v>3.33918</v>
+      </c>
+      <c r="G28">
+        <v>1.27</v>
+      </c>
+      <c r="H28">
+        <v>12.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>12.2</v>
+      </c>
+      <c r="K28">
+        <v>0.08</v>
+      </c>
+      <c r="L28">
+        <v>12.12</v>
+      </c>
+      <c r="M28">
+        <v>0.152600526</v>
+      </c>
+      <c r="N28">
+        <v>11.967399474</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>11.967399474</v>
+      </c>
+      <c r="Q28">
+        <v>12.047399474</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.174008903950514</v>
+      </c>
+      <c r="T28">
+        <v>1.833386031594266</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0.0457</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>79.42305519969176</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1407175889233804</v>
+      </c>
+      <c r="C29">
+        <v>9.350844885503513</v>
+      </c>
+      <c r="D29">
+        <v>11.54845488550351</v>
+      </c>
+      <c r="E29">
+        <v>3.12461</v>
+      </c>
+      <c r="F29">
+        <v>3.46761</v>
+      </c>
+      <c r="G29">
+        <v>1.27</v>
+      </c>
+      <c r="H29">
+        <v>12.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>12.2</v>
+      </c>
+      <c r="K29">
+        <v>0.08</v>
+      </c>
+      <c r="L29">
+        <v>12.12</v>
+      </c>
+      <c r="M29">
+        <v>0.158469777</v>
+      </c>
+      <c r="N29">
+        <v>11.961530223</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>11.961530223</v>
+      </c>
+      <c r="Q29">
+        <v>12.041530223</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1758610807169594</v>
+      </c>
+      <c r="T29">
+        <v>1.858500908739393</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0.0457</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>76.48146056266614</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1407865889233804</v>
+      </c>
+      <c r="C30">
+        <v>9.220809125102859</v>
+      </c>
+      <c r="D30">
+        <v>11.54684912510286</v>
+      </c>
+      <c r="E30">
+        <v>3.25304</v>
+      </c>
+      <c r="F30">
+        <v>3.59604</v>
+      </c>
+      <c r="G30">
+        <v>1.27</v>
+      </c>
+      <c r="H30">
+        <v>12.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>12.2</v>
+      </c>
+      <c r="K30">
+        <v>0.08</v>
+      </c>
+      <c r="L30">
+        <v>12.12</v>
+      </c>
+      <c r="M30">
+        <v>0.164339028</v>
+      </c>
+      <c r="N30">
+        <v>11.955660972</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>11.955660972</v>
+      </c>
+      <c r="Q30">
+        <v>12.035660972</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1777647068380283</v>
+      </c>
+      <c r="T30">
+        <v>1.884313421360774</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0.0457</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>73.74997982828521</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1408555889233803</v>
+      </c>
+      <c r="C31">
+        <v>9.090773811187564</v>
+      </c>
+      <c r="D31">
+        <v>11.54524381118756</v>
+      </c>
+      <c r="E31">
+        <v>3.38147</v>
+      </c>
+      <c r="F31">
+        <v>3.72447</v>
+      </c>
+      <c r="G31">
+        <v>1.27</v>
+      </c>
+      <c r="H31">
+        <v>12.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>12.2</v>
+      </c>
+      <c r="K31">
+        <v>0.08</v>
+      </c>
+      <c r="L31">
+        <v>12.12</v>
+      </c>
+      <c r="M31">
+        <v>0.170208279</v>
+      </c>
+      <c r="N31">
+        <v>11.949791721</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>11.949791721</v>
+      </c>
+      <c r="Q31">
+        <v>12.029791721</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1797219562301132</v>
+      </c>
+      <c r="T31">
+        <v>1.910853047013742</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0.0457</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>71.20687707558571</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1409245889233804</v>
+      </c>
+      <c r="C32">
+        <v>8.960738943571426</v>
+      </c>
+      <c r="D32">
+        <v>11.54363894357143</v>
+      </c>
+      <c r="E32">
+        <v>3.5099</v>
+      </c>
+      <c r="F32">
+        <v>3.8529</v>
+      </c>
+      <c r="G32">
+        <v>1.27</v>
+      </c>
+      <c r="H32">
+        <v>12.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>12.2</v>
+      </c>
+      <c r="K32">
+        <v>0.08</v>
+      </c>
+      <c r="L32">
+        <v>12.12</v>
+      </c>
+      <c r="M32">
+        <v>0.17607753</v>
+      </c>
+      <c r="N32">
+        <v>11.94392247</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>11.94392247</v>
+      </c>
+      <c r="Q32">
+        <v>12.02392247</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1817351270334005</v>
+      </c>
+      <c r="T32">
+        <v>1.938150947685367</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0.0457</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>68.83331450639953</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1409935889233804</v>
+      </c>
+      <c r="C33">
+        <v>8.830704522068361</v>
+      </c>
+      <c r="D33">
+        <v>11.54203452206836</v>
+      </c>
+      <c r="E33">
+        <v>3.63833</v>
+      </c>
+      <c r="F33">
+        <v>3.98133</v>
+      </c>
+      <c r="G33">
+        <v>1.27</v>
+      </c>
+      <c r="H33">
+        <v>12.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>12.2</v>
+      </c>
+      <c r="K33">
+        <v>0.08</v>
+      </c>
+      <c r="L33">
+        <v>12.12</v>
+      </c>
+      <c r="M33">
+        <v>0.181946781</v>
+      </c>
+      <c r="N33">
+        <v>11.938053219</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>11.938053219</v>
+      </c>
+      <c r="Q33">
+        <v>12.018053219</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1838066506135947</v>
+      </c>
+      <c r="T33">
+        <v>1.96624009185472</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0.0457</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>66.6128850061931</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1410625889233804</v>
+      </c>
+      <c r="C34">
+        <v>8.700670546492383</v>
+      </c>
+      <c r="D34">
+        <v>11.54043054649238</v>
+      </c>
+      <c r="E34">
+        <v>3.76676</v>
+      </c>
+      <c r="F34">
+        <v>4.10976</v>
+      </c>
+      <c r="G34">
+        <v>1.27</v>
+      </c>
+      <c r="H34">
+        <v>12.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>12.2</v>
+      </c>
+      <c r="K34">
+        <v>0.08</v>
+      </c>
+      <c r="L34">
+        <v>12.12</v>
+      </c>
+      <c r="M34">
+        <v>0.187816032</v>
+      </c>
+      <c r="N34">
+        <v>11.932183968</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>11.932183968</v>
+      </c>
+      <c r="Q34">
+        <v>12.012183968</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1859391013579123</v>
+      </c>
+      <c r="T34">
+        <v>1.995155387323172</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0.0457</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>64.53123234974956</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1411315889233804</v>
+      </c>
+      <c r="C35">
+        <v>8.570637016657603</v>
+      </c>
+      <c r="D35">
+        <v>11.5388270166576</v>
+      </c>
+      <c r="E35">
+        <v>3.89519</v>
+      </c>
+      <c r="F35">
+        <v>4.23819</v>
+      </c>
+      <c r="G35">
+        <v>1.27</v>
+      </c>
+      <c r="H35">
+        <v>12.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>12.2</v>
+      </c>
+      <c r="K35">
+        <v>0.08</v>
+      </c>
+      <c r="L35">
+        <v>12.12</v>
+      </c>
+      <c r="M35">
+        <v>0.193685283</v>
+      </c>
+      <c r="N35">
+        <v>11.926314717</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>11.926314717</v>
+      </c>
+      <c r="Q35">
+        <v>12.006314717</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1881352073483289</v>
+      </c>
+      <c r="T35">
+        <v>2.024933825939936</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0.0457</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>62.5757404603632</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1412005889233803</v>
+      </c>
+      <c r="C36">
+        <v>8.440603932378249</v>
+      </c>
+      <c r="D36">
+        <v>11.53722393237825</v>
+      </c>
+      <c r="E36">
+        <v>4.02362</v>
+      </c>
+      <c r="F36">
+        <v>4.36662</v>
+      </c>
+      <c r="G36">
+        <v>1.27</v>
+      </c>
+      <c r="H36">
+        <v>12.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>12.2</v>
+      </c>
+      <c r="K36">
+        <v>0.08</v>
+      </c>
+      <c r="L36">
+        <v>12.12</v>
+      </c>
+      <c r="M36">
+        <v>0.199554534</v>
+      </c>
+      <c r="N36">
+        <v>11.920445466</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>11.920445466</v>
+      </c>
+      <c r="Q36">
+        <v>12.000445466</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1903978620051218</v>
+      </c>
+      <c r="T36">
+        <v>2.05561464148448</v>
+      </c>
+      <c r="U36">
+        <v>0.0457</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0.0457</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>60.73527750564664</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1412695889233804</v>
+      </c>
+      <c r="C37">
+        <v>8.310571293468637</v>
+      </c>
+      <c r="D37">
+        <v>11.53562129346864</v>
+      </c>
+      <c r="E37">
+        <v>4.15205</v>
+      </c>
+      <c r="F37">
+        <v>4.49505</v>
+      </c>
+      <c r="G37">
+        <v>1.27</v>
+      </c>
+      <c r="H37">
+        <v>12.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>12.2</v>
+      </c>
+      <c r="K37">
+        <v>0.08</v>
+      </c>
+      <c r="L37">
+        <v>12.12</v>
+      </c>
+      <c r="M37">
+        <v>0.205423785</v>
+      </c>
+      <c r="N37">
+        <v>11.914576215</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>11.914576215</v>
+      </c>
+      <c r="Q37">
+        <v>11.994576215</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1927301368052006</v>
+      </c>
+      <c r="T37">
+        <v>2.087239482122703</v>
+      </c>
+      <c r="U37">
+        <v>0.0457</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0.0457</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>58.99998386262816</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1413385889233804</v>
+      </c>
+      <c r="C38">
+        <v>8.180539099743196</v>
+      </c>
+      <c r="D38">
+        <v>11.5340190997432</v>
+      </c>
+      <c r="E38">
+        <v>4.28048</v>
+      </c>
+      <c r="F38">
+        <v>4.62348</v>
+      </c>
+      <c r="G38">
+        <v>1.27</v>
+      </c>
+      <c r="H38">
+        <v>12.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>12.2</v>
+      </c>
+      <c r="K38">
+        <v>0.08</v>
+      </c>
+      <c r="L38">
+        <v>12.12</v>
+      </c>
+      <c r="M38">
+        <v>0.211293036</v>
+      </c>
+      <c r="N38">
+        <v>11.908706964</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>11.908706964</v>
+      </c>
+      <c r="Q38">
+        <v>11.988706964</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1951352951927818</v>
+      </c>
+      <c r="T38">
+        <v>2.11985259903087</v>
+      </c>
+      <c r="U38">
+        <v>0.0457</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0.0457</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>57.36109542199961</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1414075889233804</v>
+      </c>
+      <c r="C39">
+        <v>8.05050735101646</v>
+      </c>
+      <c r="D39">
+        <v>11.53241735101646</v>
+      </c>
+      <c r="E39">
+        <v>4.40891</v>
+      </c>
+      <c r="F39">
+        <v>4.75191</v>
+      </c>
+      <c r="G39">
+        <v>1.27</v>
+      </c>
+      <c r="H39">
+        <v>12.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>12.2</v>
+      </c>
+      <c r="K39">
+        <v>0.08</v>
+      </c>
+      <c r="L39">
+        <v>12.12</v>
+      </c>
+      <c r="M39">
+        <v>0.217162287</v>
+      </c>
+      <c r="N39">
+        <v>11.902837713</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>11.902837713</v>
+      </c>
+      <c r="Q39">
+        <v>11.982837713</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1976168078148895</v>
+      </c>
+      <c r="T39">
+        <v>2.153501052983741</v>
+      </c>
+      <c r="U39">
+        <v>0.0457</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0.0457</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>55.81079554572935</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1414765889233804</v>
+      </c>
+      <c r="C40">
+        <v>7.920476047103055</v>
+      </c>
+      <c r="D40">
+        <v>11.53081604710306</v>
+      </c>
+      <c r="E40">
+        <v>4.53734</v>
+      </c>
+      <c r="F40">
+        <v>4.88034</v>
+      </c>
+      <c r="G40">
+        <v>1.27</v>
+      </c>
+      <c r="H40">
+        <v>12.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>12.2</v>
+      </c>
+      <c r="K40">
+        <v>0.08</v>
+      </c>
+      <c r="L40">
+        <v>12.12</v>
+      </c>
+      <c r="M40">
+        <v>0.223031538</v>
+      </c>
+      <c r="N40">
+        <v>11.896968462</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>11.896968462</v>
+      </c>
+      <c r="Q40">
+        <v>11.976968462</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2001783692312586</v>
+      </c>
+      <c r="T40">
+        <v>2.188234940935092</v>
+      </c>
+      <c r="U40">
+        <v>0.0457</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0.0457</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>54.34209039978909</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1415455889233804</v>
+      </c>
+      <c r="C41">
+        <v>7.790445187817719</v>
+      </c>
+      <c r="D41">
+        <v>11.52921518781772</v>
+      </c>
+      <c r="E41">
+        <v>4.66577</v>
+      </c>
+      <c r="F41">
+        <v>5.00877</v>
+      </c>
+      <c r="G41">
+        <v>1.27</v>
+      </c>
+      <c r="H41">
+        <v>12.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>12.2</v>
+      </c>
+      <c r="K41">
+        <v>0.08</v>
+      </c>
+      <c r="L41">
+        <v>12.12</v>
+      </c>
+      <c r="M41">
+        <v>0.228900789</v>
+      </c>
+      <c r="N41">
+        <v>11.891099211</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>11.891099211</v>
+      </c>
+      <c r="Q41">
+        <v>11.971099211</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2028239162678367</v>
+      </c>
+      <c r="T41">
+        <v>2.224107644884847</v>
+      </c>
+      <c r="U41">
+        <v>0.0457</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0.0457</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>52.94870346646118</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1416145889233804</v>
+      </c>
+      <c r="C42">
+        <v>7.660414772975292</v>
+      </c>
+      <c r="D42">
+        <v>11.52761477297529</v>
+      </c>
+      <c r="E42">
+        <v>4.7942</v>
+      </c>
+      <c r="F42">
+        <v>5.1372</v>
+      </c>
+      <c r="G42">
+        <v>1.27</v>
+      </c>
+      <c r="H42">
+        <v>12.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>12.2</v>
+      </c>
+      <c r="K42">
+        <v>0.08</v>
+      </c>
+      <c r="L42">
+        <v>12.12</v>
+      </c>
+      <c r="M42">
+        <v>0.23477004</v>
+      </c>
+      <c r="N42">
+        <v>11.88522996</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>11.88522996</v>
+      </c>
+      <c r="Q42">
+        <v>11.96522996</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.205557648205634</v>
+      </c>
+      <c r="T42">
+        <v>2.261176105632928</v>
+      </c>
+      <c r="U42">
+        <v>0.0457</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0.0457</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>51.62498587979965</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1416835889233804</v>
+      </c>
+      <c r="C43">
+        <v>7.530384802390711</v>
+      </c>
+      <c r="D43">
+        <v>11.52601480239071</v>
+      </c>
+      <c r="E43">
+        <v>4.922630000000001</v>
+      </c>
+      <c r="F43">
+        <v>5.265630000000001</v>
+      </c>
+      <c r="G43">
+        <v>1.27</v>
+      </c>
+      <c r="H43">
+        <v>12.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>12.2</v>
+      </c>
+      <c r="K43">
+        <v>0.08</v>
+      </c>
+      <c r="L43">
+        <v>12.12</v>
+      </c>
+      <c r="M43">
+        <v>0.2406392910000001</v>
+      </c>
+      <c r="N43">
+        <v>11.879360709</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>11.879360709</v>
+      </c>
+      <c r="Q43">
+        <v>11.959360709</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2083840490226786</v>
+      </c>
+      <c r="T43">
+        <v>2.299501124372469</v>
+      </c>
+      <c r="U43">
+        <v>0.0457</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0.0457</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>50.36583988273135</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1417525889233804</v>
+      </c>
+      <c r="C44">
+        <v>7.400355275879027</v>
+      </c>
+      <c r="D44">
+        <v>11.52441527587903</v>
+      </c>
+      <c r="E44">
+        <v>5.05106</v>
+      </c>
+      <c r="F44">
+        <v>5.39406</v>
+      </c>
+      <c r="G44">
+        <v>1.27</v>
+      </c>
+      <c r="H44">
+        <v>12.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>12.2</v>
+      </c>
+      <c r="K44">
+        <v>0.08</v>
+      </c>
+      <c r="L44">
+        <v>12.12</v>
+      </c>
+      <c r="M44">
+        <v>0.246508542</v>
+      </c>
+      <c r="N44">
+        <v>11.873491458</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>11.873491458</v>
+      </c>
+      <c r="Q44">
+        <v>11.953491458</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2113079119368627</v>
+      </c>
+      <c r="T44">
+        <v>2.339147695482339</v>
+      </c>
+      <c r="U44">
+        <v>0.0457</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0.0457</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>49.16665321885681</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1418215889233804</v>
+      </c>
+      <c r="C45">
+        <v>7.27032619325538</v>
+      </c>
+      <c r="D45">
+        <v>11.52281619325538</v>
+      </c>
+      <c r="E45">
+        <v>5.17949</v>
+      </c>
+      <c r="F45">
+        <v>5.52249</v>
+      </c>
+      <c r="G45">
+        <v>1.27</v>
+      </c>
+      <c r="H45">
+        <v>12.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>12.2</v>
+      </c>
+      <c r="K45">
+        <v>0.08</v>
+      </c>
+      <c r="L45">
+        <v>12.12</v>
+      </c>
+      <c r="M45">
+        <v>0.252377793</v>
+      </c>
+      <c r="N45">
+        <v>11.867622207</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>11.867622207</v>
+      </c>
+      <c r="Q45">
+        <v>11.947622207</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2143343665322462</v>
+      </c>
+      <c r="T45">
+        <v>2.380185374350451</v>
+      </c>
+      <c r="U45">
+        <v>0.0457</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0.0457</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>48.02324267888339</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1418905889233804</v>
+      </c>
+      <c r="C46">
+        <v>7.140297554335022</v>
+      </c>
+      <c r="D46">
+        <v>11.52121755433502</v>
+      </c>
+      <c r="E46">
+        <v>5.30792</v>
+      </c>
+      <c r="F46">
+        <v>5.65092</v>
+      </c>
+      <c r="G46">
+        <v>1.27</v>
+      </c>
+      <c r="H46">
+        <v>12.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>12.2</v>
+      </c>
+      <c r="K46">
+        <v>0.08</v>
+      </c>
+      <c r="L46">
+        <v>12.12</v>
+      </c>
+      <c r="M46">
+        <v>0.258247044</v>
+      </c>
+      <c r="N46">
+        <v>11.861752956</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>11.861752956</v>
+      </c>
+      <c r="Q46">
+        <v>11.941752956</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2174689087917507</v>
+      </c>
+      <c r="T46">
+        <v>2.422688684606709</v>
+      </c>
+      <c r="U46">
+        <v>0.0457</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0.0457</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>46.9318053452724</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1419595889233804</v>
+      </c>
+      <c r="C47">
+        <v>7.010269358933304</v>
+      </c>
+      <c r="D47">
+        <v>11.5196193589333</v>
+      </c>
+      <c r="E47">
+        <v>5.43635</v>
+      </c>
+      <c r="F47">
+        <v>5.77935</v>
+      </c>
+      <c r="G47">
+        <v>1.27</v>
+      </c>
+      <c r="H47">
+        <v>12.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>12.2</v>
+      </c>
+      <c r="K47">
+        <v>0.08</v>
+      </c>
+      <c r="L47">
+        <v>12.12</v>
+      </c>
+      <c r="M47">
+        <v>0.264116295</v>
+      </c>
+      <c r="N47">
+        <v>11.855883705</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>11.855883705</v>
+      </c>
+      <c r="Q47">
+        <v>11.935883705</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2207174344061461</v>
+      </c>
+      <c r="T47">
+        <v>2.466737569781376</v>
+      </c>
+      <c r="U47">
+        <v>0.0457</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0.0457</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>45.88887633759969</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1420285889233804</v>
+      </c>
+      <c r="C48">
+        <v>6.880241606865682</v>
+      </c>
+      <c r="D48">
+        <v>11.51802160686568</v>
+      </c>
+      <c r="E48">
+        <v>5.56478</v>
+      </c>
+      <c r="F48">
+        <v>5.90778</v>
+      </c>
+      <c r="G48">
+        <v>1.27</v>
+      </c>
+      <c r="H48">
+        <v>12.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>12.2</v>
+      </c>
+      <c r="K48">
+        <v>0.08</v>
+      </c>
+      <c r="L48">
+        <v>12.12</v>
+      </c>
+      <c r="M48">
+        <v>0.269985546</v>
+      </c>
+      <c r="N48">
+        <v>11.850014454</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>11.850014454</v>
+      </c>
+      <c r="Q48">
+        <v>11.930014454</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2240862757840377</v>
+      </c>
+      <c r="T48">
+        <v>2.512417895147698</v>
+      </c>
+      <c r="U48">
+        <v>0.0457</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0.0457</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>44.891292069391</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1420975889233804</v>
+      </c>
+      <c r="C49">
+        <v>6.750214297947709</v>
+      </c>
+      <c r="D49">
+        <v>11.51642429794771</v>
+      </c>
+      <c r="E49">
+        <v>5.693210000000001</v>
+      </c>
+      <c r="F49">
+        <v>6.036210000000001</v>
+      </c>
+      <c r="G49">
+        <v>1.27</v>
+      </c>
+      <c r="H49">
+        <v>12.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>12.2</v>
+      </c>
+      <c r="K49">
+        <v>0.08</v>
+      </c>
+      <c r="L49">
+        <v>12.12</v>
+      </c>
+      <c r="M49">
+        <v>0.275854797</v>
+      </c>
+      <c r="N49">
+        <v>11.844145203</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>11.844145203</v>
+      </c>
+      <c r="Q49">
+        <v>11.924145203</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2275822432516611</v>
+      </c>
+      <c r="T49">
+        <v>2.5598220063769</v>
+      </c>
+      <c r="U49">
+        <v>0.0457</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0.0457</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>43.93615819557417</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1421665889233804</v>
+      </c>
+      <c r="C50">
+        <v>6.620187431995046</v>
+      </c>
+      <c r="D50">
+        <v>11.51482743199505</v>
+      </c>
+      <c r="E50">
+        <v>5.821639999999999</v>
+      </c>
+      <c r="F50">
+        <v>6.164639999999999</v>
+      </c>
+      <c r="G50">
+        <v>1.27</v>
+      </c>
+      <c r="H50">
+        <v>12.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>12.2</v>
+      </c>
+      <c r="K50">
+        <v>0.08</v>
+      </c>
+      <c r="L50">
+        <v>12.12</v>
+      </c>
+      <c r="M50">
+        <v>0.281724048</v>
+      </c>
+      <c r="N50">
+        <v>11.838275952</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>11.838275952</v>
+      </c>
+      <c r="Q50">
+        <v>11.918275952</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2312126710065007</v>
+      </c>
+      <c r="T50">
+        <v>2.609049352653379</v>
+      </c>
+      <c r="U50">
+        <v>0.0457</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0.0457</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>43.02082156649971</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1422355889233804</v>
+      </c>
+      <c r="C51">
+        <v>6.490161008823454</v>
+      </c>
+      <c r="D51">
+        <v>11.51323100882346</v>
+      </c>
+      <c r="E51">
+        <v>5.95007</v>
+      </c>
+      <c r="F51">
+        <v>6.29307</v>
+      </c>
+      <c r="G51">
+        <v>1.27</v>
+      </c>
+      <c r="H51">
+        <v>12.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>12.2</v>
+      </c>
+      <c r="K51">
+        <v>0.08</v>
+      </c>
+      <c r="L51">
+        <v>12.12</v>
+      </c>
+      <c r="M51">
+        <v>0.287593299</v>
+      </c>
+      <c r="N51">
+        <v>11.832406701</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>11.832406701</v>
+      </c>
+      <c r="Q51">
+        <v>11.912406701</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2349854684772164</v>
+      </c>
+      <c r="T51">
+        <v>2.660207183097563</v>
+      </c>
+      <c r="U51">
+        <v>0.0457</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0.0457</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>42.14284561616298</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1423045889233804</v>
+      </c>
+      <c r="C52">
+        <v>6.360135028248797</v>
+      </c>
+      <c r="D52">
+        <v>11.5116350282488</v>
+      </c>
+      <c r="E52">
+        <v>6.0785</v>
+      </c>
+      <c r="F52">
+        <v>6.4215</v>
+      </c>
+      <c r="G52">
+        <v>1.27</v>
+      </c>
+      <c r="H52">
+        <v>12.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>12.2</v>
+      </c>
+      <c r="K52">
+        <v>0.08</v>
+      </c>
+      <c r="L52">
+        <v>12.12</v>
+      </c>
+      <c r="M52">
+        <v>0.29346255</v>
+      </c>
+      <c r="N52">
+        <v>11.82653745</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>11.82653745</v>
+      </c>
+      <c r="Q52">
+        <v>11.90653745</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2389091778467607</v>
+      </c>
+      <c r="T52">
+        <v>2.713411326759514</v>
+      </c>
+      <c r="U52">
+        <v>0.0457</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0.0457</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>41.29998870383972</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1423735889233804</v>
+      </c>
+      <c r="C53">
+        <v>6.230109490087036</v>
+      </c>
+      <c r="D53">
+        <v>11.51003949008704</v>
+      </c>
+      <c r="E53">
+        <v>6.20693</v>
+      </c>
+      <c r="F53">
+        <v>6.54993</v>
+      </c>
+      <c r="G53">
+        <v>1.27</v>
+      </c>
+      <c r="H53">
+        <v>12.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>12.2</v>
+      </c>
+      <c r="K53">
+        <v>0.08</v>
+      </c>
+      <c r="L53">
+        <v>12.12</v>
+      </c>
+      <c r="M53">
+        <v>0.299331801</v>
+      </c>
+      <c r="N53">
+        <v>11.820668199</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>11.820668199</v>
+      </c>
+      <c r="Q53">
+        <v>11.900668199</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2429930386191436</v>
+      </c>
+      <c r="T53">
+        <v>2.768787068121953</v>
+      </c>
+      <c r="U53">
+        <v>0.0457</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0.0457</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>40.49018500376443</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1424425889233804</v>
+      </c>
+      <c r="C54">
+        <v>6.100084394154242</v>
+      </c>
+      <c r="D54">
+        <v>11.50844439415424</v>
+      </c>
+      <c r="E54">
+        <v>6.335360000000001</v>
+      </c>
+      <c r="F54">
+        <v>6.678360000000001</v>
+      </c>
+      <c r="G54">
+        <v>1.27</v>
+      </c>
+      <c r="H54">
+        <v>12.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>12.2</v>
+      </c>
+      <c r="K54">
+        <v>0.08</v>
+      </c>
+      <c r="L54">
+        <v>12.12</v>
+      </c>
+      <c r="M54">
+        <v>0.305201052</v>
+      </c>
+      <c r="N54">
+        <v>11.814798948</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>11.814798948</v>
+      </c>
+      <c r="Q54">
+        <v>11.894798948</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2472470602570425</v>
+      </c>
+      <c r="T54">
+        <v>2.826470132041161</v>
+      </c>
+      <c r="U54">
+        <v>0.0457</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0.0457</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>39.71152759984589</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1425115889233803</v>
+      </c>
+      <c r="C55">
+        <v>5.970059740266586</v>
+      </c>
+      <c r="D55">
+        <v>11.50684974026659</v>
+      </c>
+      <c r="E55">
+        <v>6.46379</v>
+      </c>
+      <c r="F55">
+        <v>6.80679</v>
+      </c>
+      <c r="G55">
+        <v>1.27</v>
+      </c>
+      <c r="H55">
+        <v>12.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>12.2</v>
+      </c>
+      <c r="K55">
+        <v>0.08</v>
+      </c>
+      <c r="L55">
+        <v>12.12</v>
+      </c>
+      <c r="M55">
+        <v>0.311070303</v>
+      </c>
+      <c r="N55">
+        <v>11.808929697</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>11.808929697</v>
+      </c>
+      <c r="Q55">
+        <v>11.888929697</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2516821040922986</v>
+      </c>
+      <c r="T55">
+        <v>2.886607794425015</v>
+      </c>
+      <c r="U55">
+        <v>0.0457</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0.0457</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>38.96225349418841</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1425805889233804</v>
+      </c>
+      <c r="C56">
+        <v>5.840035528240333</v>
+      </c>
+      <c r="D56">
+        <v>11.50525552824033</v>
+      </c>
+      <c r="E56">
+        <v>6.59222</v>
+      </c>
+      <c r="F56">
+        <v>6.93522</v>
+      </c>
+      <c r="G56">
+        <v>1.27</v>
+      </c>
+      <c r="H56">
+        <v>12.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>12.2</v>
+      </c>
+      <c r="K56">
+        <v>0.08</v>
+      </c>
+      <c r="L56">
+        <v>12.12</v>
+      </c>
+      <c r="M56">
+        <v>0.316939554</v>
+      </c>
+      <c r="N56">
+        <v>11.803060446</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>11.803060446</v>
+      </c>
+      <c r="Q56">
+        <v>11.883060446</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2563099759203921</v>
+      </c>
+      <c r="T56">
+        <v>2.94936013778208</v>
+      </c>
+      <c r="U56">
+        <v>0.0457</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0.0457</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>38.24073028133308</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1426495889233804</v>
+      </c>
+      <c r="C57">
+        <v>5.710011757891859</v>
+      </c>
+      <c r="D57">
+        <v>11.50366175789186</v>
+      </c>
+      <c r="E57">
+        <v>6.720650000000001</v>
+      </c>
+      <c r="F57">
+        <v>7.063650000000001</v>
+      </c>
+      <c r="G57">
+        <v>1.27</v>
+      </c>
+      <c r="H57">
+        <v>12.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>12.2</v>
+      </c>
+      <c r="K57">
+        <v>0.08</v>
+      </c>
+      <c r="L57">
+        <v>12.12</v>
+      </c>
+      <c r="M57">
+        <v>0.3228088050000001</v>
+      </c>
+      <c r="N57">
+        <v>11.797191195</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>11.797191195</v>
+      </c>
+      <c r="Q57">
+        <v>11.877191195</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2611435309408453</v>
+      </c>
+      <c r="T57">
+        <v>3.014901474177238</v>
+      </c>
+      <c r="U57">
+        <v>0.0457</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0.0457</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>37.54544427621792</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1427185889233804</v>
+      </c>
+      <c r="C58">
+        <v>5.579988429037643</v>
+      </c>
+      <c r="D58">
+        <v>11.50206842903764</v>
+      </c>
+      <c r="E58">
+        <v>6.849080000000001</v>
+      </c>
+      <c r="F58">
+        <v>7.192080000000001</v>
+      </c>
+      <c r="G58">
+        <v>1.27</v>
+      </c>
+      <c r="H58">
+        <v>12.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>12.2</v>
+      </c>
+      <c r="K58">
+        <v>0.08</v>
+      </c>
+      <c r="L58">
+        <v>12.12</v>
+      </c>
+      <c r="M58">
+        <v>0.3286780560000001</v>
+      </c>
+      <c r="N58">
+        <v>11.791321944</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>11.791321944</v>
+      </c>
+      <c r="Q58">
+        <v>11.871321944</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2661967930076827</v>
+      </c>
+      <c r="T58">
+        <v>3.08342196222672</v>
+      </c>
+      <c r="U58">
+        <v>0.0457</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0.0457</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>36.8749899141426</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1427875889233804</v>
+      </c>
+      <c r="C59">
+        <v>5.449965541494254</v>
+      </c>
+      <c r="D59">
+        <v>11.50047554149426</v>
+      </c>
+      <c r="E59">
+        <v>6.977510000000001</v>
+      </c>
+      <c r="F59">
+        <v>7.320510000000001</v>
+      </c>
+      <c r="G59">
+        <v>1.27</v>
+      </c>
+      <c r="H59">
+        <v>12.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>12.2</v>
+      </c>
+      <c r="K59">
+        <v>0.08</v>
+      </c>
+      <c r="L59">
+        <v>12.12</v>
+      </c>
+      <c r="M59">
+        <v>0.3345473070000001</v>
+      </c>
+      <c r="N59">
+        <v>11.785452693</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>11.785452693</v>
+      </c>
+      <c r="Q59">
+        <v>11.865452693</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2714850905194893</v>
+      </c>
+      <c r="T59">
+        <v>3.155129449720366</v>
+      </c>
+      <c r="U59">
+        <v>0.0457</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0.0457</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>36.22806026652606</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1428565889233804</v>
+      </c>
+      <c r="C60">
+        <v>5.319943095078375</v>
+      </c>
+      <c r="D60">
+        <v>11.49888309507837</v>
+      </c>
+      <c r="E60">
+        <v>7.105939999999999</v>
+      </c>
+      <c r="F60">
+        <v>7.448939999999999</v>
+      </c>
+      <c r="G60">
+        <v>1.27</v>
+      </c>
+      <c r="H60">
+        <v>12.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>12.2</v>
+      </c>
+      <c r="K60">
+        <v>0.08</v>
+      </c>
+      <c r="L60">
+        <v>12.12</v>
+      </c>
+      <c r="M60">
+        <v>0.340416558</v>
+      </c>
+      <c r="N60">
+        <v>11.779583442</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>11.779583442</v>
+      </c>
+      <c r="Q60">
+        <v>11.859583442</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2770252117223342</v>
+      </c>
+      <c r="T60">
+        <v>3.230251579475611</v>
+      </c>
+      <c r="U60">
+        <v>0.0457</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0.0457</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>35.60343853779286</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1429255889233804</v>
+      </c>
+      <c r="C61">
+        <v>5.189921089606785</v>
+      </c>
+      <c r="D61">
+        <v>11.49729108960678</v>
+      </c>
+      <c r="E61">
+        <v>7.234369999999999</v>
+      </c>
+      <c r="F61">
+        <v>7.577369999999999</v>
+      </c>
+      <c r="G61">
+        <v>1.27</v>
+      </c>
+      <c r="H61">
+        <v>12.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>12.2</v>
+      </c>
+      <c r="K61">
+        <v>0.08</v>
+      </c>
+      <c r="L61">
+        <v>12.12</v>
+      </c>
+      <c r="M61">
+        <v>0.346285809</v>
+      </c>
+      <c r="N61">
+        <v>11.773714191</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>11.773714191</v>
+      </c>
+      <c r="Q61">
+        <v>11.853714191</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2828355827399521</v>
+      </c>
+      <c r="T61">
+        <v>3.30903820336526</v>
+      </c>
+      <c r="U61">
+        <v>0.0457</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0.0457</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>34.99999042698282</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1429945889233804</v>
+      </c>
+      <c r="C62">
+        <v>5.059899524896361</v>
+      </c>
+      <c r="D62">
+        <v>11.49569952489636</v>
+      </c>
+      <c r="E62">
+        <v>7.3628</v>
+      </c>
+      <c r="F62">
+        <v>7.7058</v>
+      </c>
+      <c r="G62">
+        <v>1.27</v>
+      </c>
+      <c r="H62">
+        <v>12.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>12.2</v>
+      </c>
+      <c r="K62">
+        <v>0.08</v>
+      </c>
+      <c r="L62">
+        <v>12.12</v>
+      </c>
+      <c r="M62">
+        <v>0.35215506</v>
+      </c>
+      <c r="N62">
+        <v>11.76784494</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>11.76784494</v>
+      </c>
+      <c r="Q62">
+        <v>11.84784494</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2889364723084509</v>
+      </c>
+      <c r="T62">
+        <v>3.391764158449392</v>
+      </c>
+      <c r="U62">
+        <v>0.0457</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0.0457</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>34.41665725319977</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1430635889233804</v>
+      </c>
+      <c r="C63">
+        <v>4.929878400764087</v>
+      </c>
+      <c r="D63">
+        <v>11.49410840076409</v>
+      </c>
+      <c r="E63">
+        <v>7.49123</v>
+      </c>
+      <c r="F63">
+        <v>7.83423</v>
+      </c>
+      <c r="G63">
+        <v>1.27</v>
+      </c>
+      <c r="H63">
+        <v>12.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>12.2</v>
+      </c>
+      <c r="K63">
+        <v>0.08</v>
+      </c>
+      <c r="L63">
+        <v>12.12</v>
+      </c>
+      <c r="M63">
+        <v>0.358024311</v>
+      </c>
+      <c r="N63">
+        <v>11.761975689</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>11.761975689</v>
+      </c>
+      <c r="Q63">
+        <v>11.841975689</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2953502280086676</v>
+      </c>
+      <c r="T63">
+        <v>3.478732470204505</v>
+      </c>
+      <c r="U63">
+        <v>0.0457</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0.0457</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>33.85244975724567</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1431325889233804</v>
+      </c>
+      <c r="C64">
+        <v>4.799857717027049</v>
+      </c>
+      <c r="D64">
+        <v>11.49251771702705</v>
+      </c>
+      <c r="E64">
+        <v>7.61966</v>
+      </c>
+      <c r="F64">
+        <v>7.96266</v>
+      </c>
+      <c r="G64">
+        <v>1.27</v>
+      </c>
+      <c r="H64">
+        <v>12.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>12.2</v>
+      </c>
+      <c r="K64">
+        <v>0.08</v>
+      </c>
+      <c r="L64">
+        <v>12.12</v>
+      </c>
+      <c r="M64">
+        <v>0.363893562</v>
+      </c>
+      <c r="N64">
+        <v>11.756106438</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>11.756106438</v>
+      </c>
+      <c r="Q64">
+        <v>11.836106438</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3021015497983695</v>
+      </c>
+      <c r="T64">
+        <v>3.570278061525677</v>
+      </c>
+      <c r="U64">
+        <v>0.0457</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0.0457</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>33.30644250309655</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1432015889233804</v>
+      </c>
+      <c r="C65">
+        <v>4.66983747350243</v>
+      </c>
+      <c r="D65">
+        <v>11.49092747350243</v>
+      </c>
+      <c r="E65">
+        <v>7.748089999999999</v>
+      </c>
+      <c r="F65">
+        <v>8.091089999999999</v>
+      </c>
+      <c r="G65">
+        <v>1.27</v>
+      </c>
+      <c r="H65">
+        <v>12.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>12.2</v>
+      </c>
+      <c r="K65">
+        <v>0.08</v>
+      </c>
+      <c r="L65">
+        <v>12.12</v>
+      </c>
+      <c r="M65">
+        <v>0.369762813</v>
+      </c>
+      <c r="N65">
+        <v>11.750237187</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>11.750237187</v>
+      </c>
+      <c r="Q65">
+        <v>11.830237187</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.309217807901028</v>
+      </c>
+      <c r="T65">
+        <v>3.666772063188532</v>
+      </c>
+      <c r="U65">
+        <v>0.0457</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0.0457</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>32.77776881257121</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1432705889233804</v>
+      </c>
+      <c r="C66">
+        <v>4.539817670007515</v>
+      </c>
+      <c r="D66">
+        <v>11.48933767000752</v>
+      </c>
+      <c r="E66">
+        <v>7.876519999999999</v>
+      </c>
+      <c r="F66">
+        <v>8.219519999999999</v>
+      </c>
+      <c r="G66">
+        <v>1.27</v>
+      </c>
+      <c r="H66">
+        <v>12.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>12.2</v>
+      </c>
+      <c r="K66">
+        <v>0.08</v>
+      </c>
+      <c r="L66">
+        <v>12.12</v>
+      </c>
+      <c r="M66">
+        <v>0.375632064</v>
+      </c>
+      <c r="N66">
+        <v>11.744367936</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>11.744367936</v>
+      </c>
+      <c r="Q66">
+        <v>11.824367936</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3167294136760566</v>
+      </c>
+      <c r="T66">
+        <v>3.768626842721547</v>
+      </c>
+      <c r="U66">
+        <v>0.0457</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0.0457</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>32.26561617487478</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1433395889233804</v>
+      </c>
+      <c r="C67">
+        <v>4.40979830635969</v>
+      </c>
+      <c r="D67">
+        <v>11.48774830635969</v>
+      </c>
+      <c r="E67">
+        <v>8.004950000000001</v>
+      </c>
+      <c r="F67">
+        <v>8.347950000000001</v>
+      </c>
+      <c r="G67">
+        <v>1.27</v>
+      </c>
+      <c r="H67">
+        <v>12.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>12.2</v>
+      </c>
+      <c r="K67">
+        <v>0.08</v>
+      </c>
+      <c r="L67">
+        <v>12.12</v>
+      </c>
+      <c r="M67">
+        <v>0.3815013150000001</v>
+      </c>
+      <c r="N67">
+        <v>11.738498685</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>11.738498685</v>
+      </c>
+      <c r="Q67">
+        <v>11.818498685</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3246702540668011</v>
+      </c>
+      <c r="T67">
+        <v>3.876301895370735</v>
+      </c>
+      <c r="U67">
+        <v>0.0457</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0.0457</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>31.76922207987671</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1434085889233804</v>
+      </c>
+      <c r="C68">
+        <v>4.279779382376448</v>
+      </c>
+      <c r="D68">
+        <v>11.48615938237645</v>
+      </c>
+      <c r="E68">
+        <v>8.133380000000001</v>
+      </c>
+      <c r="F68">
+        <v>8.476380000000001</v>
+      </c>
+      <c r="G68">
+        <v>1.27</v>
+      </c>
+      <c r="H68">
+        <v>12.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>12.2</v>
+      </c>
+      <c r="K68">
+        <v>0.08</v>
+      </c>
+      <c r="L68">
+        <v>12.12</v>
+      </c>
+      <c r="M68">
+        <v>0.3873705660000001</v>
+      </c>
+      <c r="N68">
+        <v>11.732629434</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>11.732629434</v>
+      </c>
+      <c r="Q68">
+        <v>11.812629434</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3330782027158247</v>
+      </c>
+      <c r="T68">
+        <v>3.990310774646344</v>
+      </c>
+      <c r="U68">
+        <v>0.0457</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0.0457</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>31.2878702301816</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1434775889233804</v>
+      </c>
+      <c r="C69">
+        <v>4.149760897875376</v>
+      </c>
+      <c r="D69">
+        <v>11.48457089787538</v>
+      </c>
+      <c r="E69">
+        <v>8.261810000000001</v>
+      </c>
+      <c r="F69">
+        <v>8.604810000000001</v>
+      </c>
+      <c r="G69">
+        <v>1.27</v>
+      </c>
+      <c r="H69">
+        <v>12.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>12.2</v>
+      </c>
+      <c r="K69">
+        <v>0.08</v>
+      </c>
+      <c r="L69">
+        <v>12.12</v>
+      </c>
+      <c r="M69">
+        <v>0.393239817</v>
+      </c>
+      <c r="N69">
+        <v>11.726760183</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>11.726760183</v>
+      </c>
+      <c r="Q69">
+        <v>11.806760183</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.3419957240102436</v>
+      </c>
+      <c r="T69">
+        <v>4.111229282968961</v>
+      </c>
+      <c r="U69">
+        <v>0.0457</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0.0457</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>30.8208870924177</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1435465889233804</v>
+      </c>
+      <c r="C70">
+        <v>4.019742852674163</v>
+      </c>
+      <c r="D70">
+        <v>11.48298285267416</v>
+      </c>
+      <c r="E70">
+        <v>8.39024</v>
+      </c>
+      <c r="F70">
+        <v>8.73324</v>
+      </c>
+      <c r="G70">
+        <v>1.27</v>
+      </c>
+      <c r="H70">
+        <v>12.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>12.2</v>
+      </c>
+      <c r="K70">
+        <v>0.08</v>
+      </c>
+      <c r="L70">
+        <v>12.12</v>
+      </c>
+      <c r="M70">
+        <v>0.3991090680000001</v>
+      </c>
+      <c r="N70">
+        <v>11.720890932</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>11.720890932</v>
+      </c>
+      <c r="Q70">
+        <v>11.800890932</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3514705903855637</v>
+      </c>
+      <c r="T70">
+        <v>4.239705198061741</v>
+      </c>
+      <c r="U70">
+        <v>0.0457</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0.0457</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>30.36763875282332</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1436155889233804</v>
+      </c>
+      <c r="C71">
+        <v>3.889725246590599</v>
+      </c>
+      <c r="D71">
+        <v>11.4813952465906</v>
+      </c>
+      <c r="E71">
+        <v>8.51867</v>
+      </c>
+      <c r="F71">
+        <v>8.86167</v>
+      </c>
+      <c r="G71">
+        <v>1.27</v>
+      </c>
+      <c r="H71">
+        <v>12.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>12.2</v>
+      </c>
+      <c r="K71">
+        <v>0.08</v>
+      </c>
+      <c r="L71">
+        <v>12.12</v>
+      </c>
+      <c r="M71">
+        <v>0.404978319</v>
+      </c>
+      <c r="N71">
+        <v>11.715021681</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>11.715021681</v>
+      </c>
+      <c r="Q71">
+        <v>11.795021681</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3615567384625175</v>
+      </c>
+      <c r="T71">
+        <v>4.376469881870185</v>
+      </c>
+      <c r="U71">
+        <v>0.0457</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0.0457</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>29.92752804626067</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1436845889233804</v>
+      </c>
+      <c r="C72">
+        <v>3.759708079442577</v>
+      </c>
+      <c r="D72">
+        <v>11.47980807944258</v>
+      </c>
+      <c r="E72">
+        <v>8.6471</v>
+      </c>
+      <c r="F72">
+        <v>8.9901</v>
+      </c>
+      <c r="G72">
+        <v>1.27</v>
+      </c>
+      <c r="H72">
+        <v>12.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>12.2</v>
+      </c>
+      <c r="K72">
+        <v>0.08</v>
+      </c>
+      <c r="L72">
+        <v>12.12</v>
+      </c>
+      <c r="M72">
+        <v>0.4108475700000001</v>
+      </c>
+      <c r="N72">
+        <v>11.70915243</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>11.70915243</v>
+      </c>
+      <c r="Q72">
+        <v>11.78915243</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3723152964112679</v>
+      </c>
+      <c r="T72">
+        <v>4.522352211265857</v>
+      </c>
+      <c r="U72">
+        <v>0.0457</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0.0457</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>29.49999193131409</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1437535889233804</v>
+      </c>
+      <c r="C73">
+        <v>3.629691351048089</v>
+      </c>
+      <c r="D73">
+        <v>11.47822135104809</v>
+      </c>
+      <c r="E73">
+        <v>8.77553</v>
+      </c>
+      <c r="F73">
+        <v>9.11853</v>
+      </c>
+      <c r="G73">
+        <v>1.27</v>
+      </c>
+      <c r="H73">
+        <v>12.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>12.2</v>
+      </c>
+      <c r="K73">
+        <v>0.08</v>
+      </c>
+      <c r="L73">
+        <v>12.12</v>
+      </c>
+      <c r="M73">
+        <v>0.416716821</v>
+      </c>
+      <c r="N73">
+        <v>11.703283179</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>11.703283179</v>
+      </c>
+      <c r="Q73">
+        <v>11.783283179</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3838158238737254</v>
+      </c>
+      <c r="T73">
+        <v>4.678295390964679</v>
+      </c>
+      <c r="U73">
+        <v>0.0457</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0.0457</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>29.08449908721107</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1438225889233804</v>
+      </c>
+      <c r="C74">
+        <v>3.499675061225226</v>
+      </c>
+      <c r="D74">
+        <v>11.47663506122523</v>
+      </c>
+      <c r="E74">
+        <v>8.90396</v>
+      </c>
+      <c r="F74">
+        <v>9.24696</v>
+      </c>
+      <c r="G74">
+        <v>1.27</v>
+      </c>
+      <c r="H74">
+        <v>12.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>12.2</v>
+      </c>
+      <c r="K74">
+        <v>0.08</v>
+      </c>
+      <c r="L74">
+        <v>12.12</v>
+      </c>
+      <c r="M74">
+        <v>0.422586072</v>
+      </c>
+      <c r="N74">
+        <v>11.697413928</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>11.697413928</v>
+      </c>
+      <c r="Q74">
+        <v>11.777413928</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3961378175835013</v>
+      </c>
+      <c r="T74">
+        <v>4.845377369213417</v>
+      </c>
+      <c r="U74">
+        <v>0.0457</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0.0457</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>28.6805477109998</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1438915889233804</v>
+      </c>
+      <c r="C75">
+        <v>3.369659209792184</v>
+      </c>
+      <c r="D75">
+        <v>11.47504920979218</v>
+      </c>
+      <c r="E75">
+        <v>9.032389999999999</v>
+      </c>
+      <c r="F75">
+        <v>9.375389999999999</v>
+      </c>
+      <c r="G75">
+        <v>1.27</v>
+      </c>
+      <c r="H75">
+        <v>12.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>12.2</v>
+      </c>
+      <c r="K75">
+        <v>0.08</v>
+      </c>
+      <c r="L75">
+        <v>12.12</v>
+      </c>
+      <c r="M75">
+        <v>0.428455323</v>
+      </c>
+      <c r="N75">
+        <v>11.691544677</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>11.691544677</v>
+      </c>
+      <c r="Q75">
+        <v>11.771544677</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4093725515680754</v>
+      </c>
+      <c r="T75">
+        <v>5.024835790295396</v>
+      </c>
+      <c r="U75">
+        <v>0.0457</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0.0457</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>28.28766349578063</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1439605889233804</v>
+      </c>
+      <c r="C76">
+        <v>3.239643796567256</v>
+      </c>
+      <c r="D76">
+        <v>11.47346379656726</v>
+      </c>
+      <c r="E76">
+        <v>9.160819999999999</v>
+      </c>
+      <c r="F76">
+        <v>9.503819999999999</v>
+      </c>
+      <c r="G76">
+        <v>1.27</v>
+      </c>
+      <c r="H76">
+        <v>12.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>12.2</v>
+      </c>
+      <c r="K76">
+        <v>0.08</v>
+      </c>
+      <c r="L76">
+        <v>12.12</v>
+      </c>
+      <c r="M76">
+        <v>0.434324574</v>
+      </c>
+      <c r="N76">
+        <v>11.685675426</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>11.685675426</v>
+      </c>
+      <c r="Q76">
+        <v>11.765675426</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.4236253420130014</v>
+      </c>
+      <c r="T76">
+        <v>5.218098705306757</v>
+      </c>
+      <c r="U76">
+        <v>0.0457</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0.0457</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>27.90539777286467</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1440295889233804</v>
+      </c>
+      <c r="C77">
+        <v>3.109628821368835</v>
+      </c>
+      <c r="D77">
+        <v>11.47187882136883</v>
+      </c>
+      <c r="E77">
+        <v>9.289249999999999</v>
+      </c>
+      <c r="F77">
+        <v>9.632249999999999</v>
+      </c>
+      <c r="G77">
+        <v>1.27</v>
+      </c>
+      <c r="H77">
+        <v>12.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>12.2</v>
+      </c>
+      <c r="K77">
+        <v>0.08</v>
+      </c>
+      <c r="L77">
+        <v>12.12</v>
+      </c>
+      <c r="M77">
+        <v>0.440193825</v>
+      </c>
+      <c r="N77">
+        <v>11.679806175</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>11.679806175</v>
+      </c>
+      <c r="Q77">
+        <v>11.759806175</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4390183556935215</v>
+      </c>
+      <c r="T77">
+        <v>5.426822653519028</v>
+      </c>
+      <c r="U77">
+        <v>0.0457</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0.0457</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>27.53332580255982</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1440985889233804</v>
+      </c>
+      <c r="C78">
+        <v>2.979614284015417</v>
+      </c>
+      <c r="D78">
+        <v>11.47029428401542</v>
+      </c>
+      <c r="E78">
+        <v>9.417680000000001</v>
+      </c>
+      <c r="F78">
+        <v>9.760680000000001</v>
+      </c>
+      <c r="G78">
+        <v>1.27</v>
+      </c>
+      <c r="H78">
+        <v>12.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>12.2</v>
+      </c>
+      <c r="K78">
+        <v>0.08</v>
+      </c>
+      <c r="L78">
+        <v>12.12</v>
+      </c>
+      <c r="M78">
+        <v>0.4460630760000001</v>
+      </c>
+      <c r="N78">
+        <v>11.673936924</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>11.673936924</v>
+      </c>
+      <c r="Q78">
+        <v>11.753936924</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4556941205140849</v>
+      </c>
+      <c r="T78">
+        <v>5.652940264082321</v>
+      </c>
+      <c r="U78">
+        <v>0.0457</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0.0457</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>27.17104519989455</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1441675889233804</v>
+      </c>
+      <c r="C79">
+        <v>2.849600184325597</v>
+      </c>
+      <c r="D79">
+        <v>11.4687101843256</v>
+      </c>
+      <c r="E79">
+        <v>9.546110000000001</v>
+      </c>
+      <c r="F79">
+        <v>9.889110000000001</v>
+      </c>
+      <c r="G79">
+        <v>1.27</v>
+      </c>
+      <c r="H79">
+        <v>12.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>12.2</v>
+      </c>
+      <c r="K79">
+        <v>0.08</v>
+      </c>
+      <c r="L79">
+        <v>12.12</v>
+      </c>
+      <c r="M79">
+        <v>0.4519323270000001</v>
+      </c>
+      <c r="N79">
+        <v>11.668067673</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>11.668067673</v>
+      </c>
+      <c r="Q79">
+        <v>11.748067673</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4738199518407842</v>
+      </c>
+      <c r="T79">
+        <v>5.898720275564161</v>
+      </c>
+      <c r="U79">
+        <v>0.0457</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0.0457</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>26.8181744830128</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1442365889233804</v>
+      </c>
+      <c r="C80">
+        <v>2.719586522118068</v>
+      </c>
+      <c r="D80">
+        <v>11.46712652211807</v>
+      </c>
+      <c r="E80">
+        <v>9.67454</v>
+      </c>
+      <c r="F80">
+        <v>10.01754</v>
+      </c>
+      <c r="G80">
+        <v>1.27</v>
+      </c>
+      <c r="H80">
+        <v>12.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>12.2</v>
+      </c>
+      <c r="K80">
+        <v>0.08</v>
+      </c>
+      <c r="L80">
+        <v>12.12</v>
+      </c>
+      <c r="M80">
+        <v>0.457801578</v>
+      </c>
+      <c r="N80">
+        <v>11.662198422</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>11.662198422</v>
+      </c>
+      <c r="Q80">
+        <v>11.742198422</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4935935860153653</v>
+      </c>
+      <c r="T80">
+        <v>6.166843924453441</v>
+      </c>
+      <c r="U80">
+        <v>0.0457</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0.0457</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>26.47435173323059</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1443055889233804</v>
+      </c>
+      <c r="C81">
+        <v>2.589573297211627</v>
+      </c>
+      <c r="D81">
+        <v>11.46554329721163</v>
+      </c>
+      <c r="E81">
+        <v>9.80297</v>
+      </c>
+      <c r="F81">
+        <v>10.14597</v>
+      </c>
+      <c r="G81">
+        <v>1.27</v>
+      </c>
+      <c r="H81">
+        <v>12.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>12.2</v>
+      </c>
+      <c r="K81">
+        <v>0.08</v>
+      </c>
+      <c r="L81">
+        <v>12.12</v>
+      </c>
+      <c r="M81">
+        <v>0.4636708290000001</v>
+      </c>
+      <c r="N81">
+        <v>11.656329171</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>11.656329171</v>
+      </c>
+      <c r="Q81">
+        <v>11.736329171</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.5152504234446685</v>
+      </c>
+      <c r="T81">
+        <v>6.460503158951225</v>
+      </c>
+      <c r="U81">
+        <v>0.0457</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0.0457</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>26.13923335686058</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1443745889233804</v>
+      </c>
+      <c r="C82">
+        <v>2.459560509425172</v>
+      </c>
+      <c r="D82">
+        <v>11.46396050942517</v>
+      </c>
+      <c r="E82">
+        <v>9.9314</v>
+      </c>
+      <c r="F82">
+        <v>10.2744</v>
+      </c>
+      <c r="G82">
+        <v>1.27</v>
+      </c>
+      <c r="H82">
+        <v>12.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>12.2</v>
+      </c>
+      <c r="K82">
+        <v>0.08</v>
+      </c>
+      <c r="L82">
+        <v>12.12</v>
+      </c>
+      <c r="M82">
+        <v>0.46954008</v>
+      </c>
+      <c r="N82">
+        <v>11.65045992</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>11.65045992</v>
+      </c>
+      <c r="Q82">
+        <v>11.73045992</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.539072944616902</v>
+      </c>
+      <c r="T82">
+        <v>6.783528316898786</v>
+      </c>
+      <c r="U82">
+        <v>0.0457</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0.0457</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>25.81249293989983</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1444435889233804</v>
+      </c>
+      <c r="C83">
+        <v>2.32954815857769</v>
+      </c>
+      <c r="D83">
+        <v>11.46237815857769</v>
+      </c>
+      <c r="E83">
+        <v>10.05983</v>
+      </c>
+      <c r="F83">
+        <v>10.40283</v>
+      </c>
+      <c r="G83">
+        <v>1.27</v>
+      </c>
+      <c r="H83">
+        <v>12.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>12.2</v>
+      </c>
+      <c r="K83">
+        <v>0.08</v>
+      </c>
+      <c r="L83">
+        <v>12.12</v>
+      </c>
+      <c r="M83">
+        <v>0.475409331</v>
+      </c>
+      <c r="N83">
+        <v>11.644590669</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>11.644590669</v>
+      </c>
+      <c r="Q83">
+        <v>11.724590669</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.565403099596739</v>
+      </c>
+      <c r="T83">
+        <v>7.140556123051354</v>
+      </c>
+      <c r="U83">
+        <v>0.0457</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0.0457</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>25.49382018755538</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1445125889233804</v>
+      </c>
+      <c r="C84">
+        <v>2.199536244488284</v>
+      </c>
+      <c r="D84">
+        <v>11.46079624448829</v>
+      </c>
+      <c r="E84">
+        <v>10.18826</v>
+      </c>
+      <c r="F84">
+        <v>10.53126</v>
+      </c>
+      <c r="G84">
+        <v>1.27</v>
+      </c>
+      <c r="H84">
+        <v>12.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>12.2</v>
+      </c>
+      <c r="K84">
+        <v>0.08</v>
+      </c>
+      <c r="L84">
+        <v>12.12</v>
+      </c>
+      <c r="M84">
+        <v>0.4812785820000001</v>
+      </c>
+      <c r="N84">
+        <v>11.638721418</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>11.638721418</v>
+      </c>
+      <c r="Q84">
+        <v>11.718721418</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5946588273521134</v>
+      </c>
+      <c r="T84">
+        <v>7.537253685443097</v>
+      </c>
+      <c r="U84">
+        <v>0.0457</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0.0457</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>25.18291994136568</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1445815889233804</v>
+      </c>
+      <c r="C85">
+        <v>2.069524766976146</v>
+      </c>
+      <c r="D85">
+        <v>11.45921476697615</v>
+      </c>
+      <c r="E85">
+        <v>10.31669</v>
+      </c>
+      <c r="F85">
+        <v>10.65969</v>
+      </c>
+      <c r="G85">
+        <v>1.27</v>
+      </c>
+      <c r="H85">
+        <v>12.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>12.2</v>
+      </c>
+      <c r="K85">
+        <v>0.08</v>
+      </c>
+      <c r="L85">
+        <v>12.12</v>
+      </c>
+      <c r="M85">
+        <v>0.4871478330000001</v>
+      </c>
+      <c r="N85">
+        <v>11.632852167</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>11.632852167</v>
+      </c>
+      <c r="Q85">
+        <v>11.712852167</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.6273564054316494</v>
+      </c>
+      <c r="T85">
+        <v>7.980621549292691</v>
+      </c>
+      <c r="U85">
+        <v>0.0457</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0.0457</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>24.87951126737332</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1446505889233804</v>
+      </c>
+      <c r="C86">
+        <v>1.939513725860573</v>
+      </c>
+      <c r="D86">
+        <v>11.45763372586057</v>
+      </c>
+      <c r="E86">
+        <v>10.44512</v>
+      </c>
+      <c r="F86">
+        <v>10.78812</v>
+      </c>
+      <c r="G86">
+        <v>1.27</v>
+      </c>
+      <c r="H86">
+        <v>12.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>12.2</v>
+      </c>
+      <c r="K86">
+        <v>0.08</v>
+      </c>
+      <c r="L86">
+        <v>12.12</v>
+      </c>
+      <c r="M86">
+        <v>0.493017084</v>
+      </c>
+      <c r="N86">
+        <v>11.626982916</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>11.626982916</v>
+      </c>
+      <c r="Q86">
+        <v>11.706982916</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6641411807711273</v>
+      </c>
+      <c r="T86">
+        <v>8.47941039612348</v>
+      </c>
+      <c r="U86">
+        <v>0.0457</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0.0457</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>24.5833266094284</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1447195889233804</v>
+      </c>
+      <c r="C87">
+        <v>1.809503120960956</v>
+      </c>
+      <c r="D87">
+        <v>11.45605312096096</v>
+      </c>
+      <c r="E87">
+        <v>10.57355</v>
+      </c>
+      <c r="F87">
+        <v>10.91655</v>
+      </c>
+      <c r="G87">
+        <v>1.27</v>
+      </c>
+      <c r="H87">
+        <v>12.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>12.2</v>
+      </c>
+      <c r="K87">
+        <v>0.08</v>
+      </c>
+      <c r="L87">
+        <v>12.12</v>
+      </c>
+      <c r="M87">
+        <v>0.498886335</v>
+      </c>
+      <c r="N87">
+        <v>11.621113665</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>11.621113665</v>
+      </c>
+      <c r="Q87">
+        <v>11.701113665</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.7058305928225357</v>
+      </c>
+      <c r="T87">
+        <v>9.044704422531712</v>
+      </c>
+      <c r="U87">
+        <v>0.0457</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0.0457</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>24.29411100225866</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1447885889233804</v>
+      </c>
+      <c r="C88">
+        <v>1.679492952096791</v>
+      </c>
+      <c r="D88">
+        <v>11.45447295209679</v>
+      </c>
+      <c r="E88">
+        <v>10.70198</v>
+      </c>
+      <c r="F88">
+        <v>11.04498</v>
+      </c>
+      <c r="G88">
+        <v>1.27</v>
+      </c>
+      <c r="H88">
+        <v>12.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>12.2</v>
+      </c>
+      <c r="K88">
+        <v>0.08</v>
+      </c>
+      <c r="L88">
+        <v>12.12</v>
+      </c>
+      <c r="M88">
+        <v>0.504755586</v>
+      </c>
+      <c r="N88">
+        <v>11.615244414</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>11.615244414</v>
+      </c>
+      <c r="Q88">
+        <v>11.695244414</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.7534756351670027</v>
+      </c>
+      <c r="T88">
+        <v>9.690754738426834</v>
+      </c>
+      <c r="U88">
+        <v>0.0457</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88">
+        <v>0.0457</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>24.0116213394417</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1448575889233804</v>
+      </c>
+      <c r="C89">
+        <v>1.549483219087671</v>
+      </c>
+      <c r="D89">
+        <v>11.45289321908767</v>
+      </c>
+      <c r="E89">
+        <v>10.83041</v>
+      </c>
+      <c r="F89">
+        <v>11.17341</v>
+      </c>
+      <c r="G89">
+        <v>1.27</v>
+      </c>
+      <c r="H89">
+        <v>12.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>12.2</v>
+      </c>
+      <c r="K89">
+        <v>0.08</v>
+      </c>
+      <c r="L89">
+        <v>12.12</v>
+      </c>
+      <c r="M89">
+        <v>0.5106248370000001</v>
+      </c>
+      <c r="N89">
+        <v>11.609375163</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>11.609375163</v>
+      </c>
+      <c r="Q89">
+        <v>11.689375163</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.8084506840260028</v>
+      </c>
+      <c r="T89">
+        <v>10.43619741061351</v>
+      </c>
+      <c r="U89">
+        <v>0.0457</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>0.0457</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>23.73562569186191</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1449265889233804</v>
+      </c>
+      <c r="C90">
+        <v>1.419473921753291</v>
+      </c>
+      <c r="D90">
+        <v>11.45131392175329</v>
+      </c>
+      <c r="E90">
+        <v>10.95884</v>
+      </c>
+      <c r="F90">
+        <v>11.30184</v>
+      </c>
+      <c r="G90">
+        <v>1.27</v>
+      </c>
+      <c r="H90">
+        <v>12.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>12.2</v>
+      </c>
+      <c r="K90">
+        <v>0.08</v>
+      </c>
+      <c r="L90">
+        <v>12.12</v>
+      </c>
+      <c r="M90">
+        <v>0.5164940880000001</v>
+      </c>
+      <c r="N90">
+        <v>11.603505912</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>11.603505912</v>
+      </c>
+      <c r="Q90">
+        <v>11.683505912</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.8725882410281698</v>
+      </c>
+      <c r="T90">
+        <v>11.30588052816464</v>
+      </c>
+      <c r="U90">
+        <v>0.0457</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>0.0457</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>23.4659026726362</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1449955889233804</v>
+      </c>
+      <c r="C91">
+        <v>1.289465059913441</v>
+      </c>
+      <c r="D91">
+        <v>11.44973505991344</v>
+      </c>
+      <c r="E91">
+        <v>11.08727</v>
+      </c>
+      <c r="F91">
+        <v>11.43027</v>
+      </c>
+      <c r="G91">
+        <v>1.27</v>
+      </c>
+      <c r="H91">
+        <v>12.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>12.2</v>
+      </c>
+      <c r="K91">
+        <v>0.08</v>
+      </c>
+      <c r="L91">
+        <v>12.12</v>
+      </c>
+      <c r="M91">
+        <v>0.5223633390000001</v>
+      </c>
+      <c r="N91">
+        <v>11.597636661</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>11.597636661</v>
+      </c>
+      <c r="Q91">
+        <v>11.677636661</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.9483871720307306</v>
+      </c>
+      <c r="T91">
+        <v>12.33368784890688</v>
+      </c>
+      <c r="U91">
+        <v>0.0457</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0.0457</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>23.20224084485377</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1450645889233804</v>
+      </c>
+      <c r="C92">
+        <v>1.159456633388015</v>
+      </c>
+      <c r="D92">
+        <v>11.44815663338801</v>
+      </c>
+      <c r="E92">
+        <v>11.2157</v>
+      </c>
+      <c r="F92">
+        <v>11.5587</v>
+      </c>
+      <c r="G92">
+        <v>1.27</v>
+      </c>
+      <c r="H92">
+        <v>12.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>12.2</v>
+      </c>
+      <c r="K92">
+        <v>0.08</v>
+      </c>
+      <c r="L92">
+        <v>12.12</v>
+      </c>
+      <c r="M92">
+        <v>0.52823259</v>
+      </c>
+      <c r="N92">
+        <v>11.59176741</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>11.59176741</v>
+      </c>
+      <c r="Q92">
+        <v>11.67176741</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.039345889233804</v>
+      </c>
+      <c r="T92">
+        <v>13.56705663379757</v>
+      </c>
+      <c r="U92">
+        <v>0.0457</v>
+      </c>
+      <c r="V92">
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <v>0.0457</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>22.94443816879985</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1451335889233804</v>
+      </c>
+      <c r="C93">
+        <v>1.029448641997003</v>
+      </c>
+      <c r="D93">
+        <v>11.446578641997</v>
+      </c>
+      <c r="E93">
+        <v>11.34413</v>
+      </c>
+      <c r="F93">
+        <v>11.68713</v>
+      </c>
+      <c r="G93">
+        <v>1.27</v>
+      </c>
+      <c r="H93">
+        <v>12.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>12.2</v>
+      </c>
+      <c r="K93">
+        <v>0.08</v>
+      </c>
+      <c r="L93">
+        <v>12.12</v>
+      </c>
+      <c r="M93">
+        <v>0.534101841</v>
+      </c>
+      <c r="N93">
+        <v>11.585898159</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>11.585898159</v>
+      </c>
+      <c r="Q93">
+        <v>11.665898159</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.150517654704227</v>
+      </c>
+      <c r="T93">
+        <v>15.07450737088619</v>
+      </c>
+      <c r="U93">
+        <v>0.0457</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <v>0.0457</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>22.69230148562622</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1452025889233804</v>
+      </c>
+      <c r="C94">
+        <v>0.8994410855604968</v>
+      </c>
+      <c r="D94">
+        <v>11.4450010855605</v>
+      </c>
+      <c r="E94">
+        <v>11.47256</v>
+      </c>
+      <c r="F94">
+        <v>11.81556</v>
+      </c>
+      <c r="G94">
+        <v>1.27</v>
+      </c>
+      <c r="H94">
+        <v>12.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>12.2</v>
+      </c>
+      <c r="K94">
+        <v>0.08</v>
+      </c>
+      <c r="L94">
+        <v>12.12</v>
+      </c>
+      <c r="M94">
+        <v>0.539971092</v>
+      </c>
+      <c r="N94">
+        <v>11.580028908</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>11.580028908</v>
+      </c>
+      <c r="Q94">
+        <v>11.660028908</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.289482361542255</v>
+      </c>
+      <c r="T94">
+        <v>16.95882079224697</v>
+      </c>
+      <c r="U94">
+        <v>0.0457</v>
+      </c>
+      <c r="V94">
+        <v>0</v>
+      </c>
+      <c r="W94">
+        <v>0.0457</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>22.4456460346955</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1452715889233804</v>
+      </c>
+      <c r="C95">
+        <v>0.7694339638986847</v>
+      </c>
+      <c r="D95">
+        <v>11.44342396389869</v>
+      </c>
+      <c r="E95">
+        <v>11.60099</v>
+      </c>
+      <c r="F95">
+        <v>11.94399</v>
+      </c>
+      <c r="G95">
+        <v>1.27</v>
+      </c>
+      <c r="H95">
+        <v>12.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>12.2</v>
+      </c>
+      <c r="K95">
+        <v>0.08</v>
+      </c>
+      <c r="L95">
+        <v>12.12</v>
+      </c>
+      <c r="M95">
+        <v>0.5458403430000001</v>
+      </c>
+      <c r="N95">
+        <v>11.574159657</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>11.574159657</v>
+      </c>
+      <c r="Q95">
+        <v>11.654159657</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.468151270334006</v>
+      </c>
+      <c r="T95">
+        <v>19.38150947685368</v>
+      </c>
+      <c r="U95">
+        <v>0.0457</v>
+      </c>
+      <c r="V95">
+        <v>0</v>
+      </c>
+      <c r="W95">
+        <v>0.0457</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>22.20429500206436</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1453405889233804</v>
+      </c>
+      <c r="C96">
+        <v>0.6394272768318583</v>
+      </c>
+      <c r="D96">
+        <v>11.44184727683186</v>
+      </c>
+      <c r="E96">
+        <v>11.72942</v>
+      </c>
+      <c r="F96">
+        <v>12.07242</v>
+      </c>
+      <c r="G96">
+        <v>1.27</v>
+      </c>
+      <c r="H96">
+        <v>12.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>12.2</v>
+      </c>
+      <c r="K96">
+        <v>0.08</v>
+      </c>
+      <c r="L96">
+        <v>12.12</v>
+      </c>
+      <c r="M96">
+        <v>0.5517095940000001</v>
+      </c>
+      <c r="N96">
+        <v>11.568290406</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>11.568290406</v>
+      </c>
+      <c r="Q96">
+        <v>11.648290406</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.706376482056341</v>
+      </c>
+      <c r="T96">
+        <v>22.6117610563293</v>
+      </c>
+      <c r="U96">
+        <v>0.0457</v>
+      </c>
+      <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="W96">
+        <v>0.0457</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>21.96807909778708</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1454095889233804</v>
+      </c>
+      <c r="C97">
+        <v>0.5094210241804031</v>
+      </c>
+      <c r="D97">
+        <v>11.4402710241804</v>
+      </c>
+      <c r="E97">
+        <v>11.85785</v>
+      </c>
+      <c r="F97">
+        <v>12.20085</v>
+      </c>
+      <c r="G97">
+        <v>1.27</v>
+      </c>
+      <c r="H97">
+        <v>12.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>12.2</v>
+      </c>
+      <c r="K97">
+        <v>0.08</v>
+      </c>
+      <c r="L97">
+        <v>12.12</v>
+      </c>
+      <c r="M97">
+        <v>0.5575788450000001</v>
+      </c>
+      <c r="N97">
+        <v>11.562421155</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>11.562421155</v>
+      </c>
+      <c r="Q97">
+        <v>11.642421155</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.039891778467611</v>
+      </c>
+      <c r="T97">
+        <v>27.13411326759518</v>
+      </c>
+      <c r="U97">
+        <v>0.0457</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97">
+        <v>0.0457</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>21.73683615991564</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1454785889233804</v>
+      </c>
+      <c r="C98">
+        <v>0.3794152057648095</v>
+      </c>
+      <c r="D98">
+        <v>11.43869520576481</v>
+      </c>
+      <c r="E98">
+        <v>11.98628</v>
+      </c>
+      <c r="F98">
+        <v>12.32928</v>
+      </c>
+      <c r="G98">
+        <v>1.27</v>
+      </c>
+      <c r="H98">
+        <v>12.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>12.2</v>
+      </c>
+      <c r="K98">
+        <v>0.08</v>
+      </c>
+      <c r="L98">
+        <v>12.12</v>
+      </c>
+      <c r="M98">
+        <v>0.563448096</v>
+      </c>
+      <c r="N98">
+        <v>11.556551904</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>11.556551904</v>
+      </c>
+      <c r="Q98">
+        <v>11.636551904</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.540164723084507</v>
+      </c>
+      <c r="T98">
+        <v>33.91764158449389</v>
+      </c>
+      <c r="U98">
+        <v>0.0457</v>
+      </c>
+      <c r="V98">
+        <v>0</v>
+      </c>
+      <c r="W98">
+        <v>0.0457</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>21.51041078324985</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1455475889233804</v>
+      </c>
+      <c r="C99">
+        <v>0.2494098214056546</v>
+      </c>
+      <c r="D99">
+        <v>11.43711982140566</v>
+      </c>
+      <c r="E99">
+        <v>12.11471</v>
+      </c>
+      <c r="F99">
+        <v>12.45771</v>
+      </c>
+      <c r="G99">
+        <v>1.27</v>
+      </c>
+      <c r="H99">
+        <v>12.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>12.2</v>
+      </c>
+      <c r="K99">
+        <v>0.08</v>
+      </c>
+      <c r="L99">
+        <v>12.12</v>
+      </c>
+      <c r="M99">
+        <v>0.569317347</v>
+      </c>
+      <c r="N99">
+        <v>11.550682653</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>11.550682653</v>
+      </c>
+      <c r="Q99">
+        <v>11.630682653</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.373952964112676</v>
+      </c>
+      <c r="T99">
+        <v>45.22352211265853</v>
+      </c>
+      <c r="U99">
+        <v>0.0457</v>
+      </c>
+      <c r="V99">
+        <v>0</v>
+      </c>
+      <c r="W99">
+        <v>0.0457</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>21.2886539710514</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1456165889233804</v>
+      </c>
+      <c r="C100">
+        <v>0.1194048709236331</v>
+      </c>
+      <c r="D100">
+        <v>11.43554487092363</v>
+      </c>
+      <c r="E100">
+        <v>12.24314</v>
+      </c>
+      <c r="F100">
+        <v>12.58614</v>
+      </c>
+      <c r="G100">
+        <v>1.27</v>
+      </c>
+      <c r="H100">
+        <v>12.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>12.2</v>
+      </c>
+      <c r="K100">
+        <v>0.08</v>
+      </c>
+      <c r="L100">
+        <v>12.12</v>
+      </c>
+      <c r="M100">
+        <v>0.575186598</v>
+      </c>
+      <c r="N100">
+        <v>11.544813402</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>11.544813402</v>
+      </c>
+      <c r="Q100">
+        <v>11.624813402</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>5.041529446169014</v>
+      </c>
+      <c r="T100">
+        <v>67.83528316898779</v>
+      </c>
+      <c r="U100">
+        <v>0.0457</v>
+      </c>
+      <c r="V100">
+        <v>0</v>
+      </c>
+      <c r="W100">
+        <v>0.0457</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>21.07142280808149</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1456855889233804</v>
+      </c>
+      <c r="C101">
+        <v>-0.0105996458604789</v>
+      </c>
+      <c r="D101">
+        <v>11.43397035413952</v>
+      </c>
+      <c r="E101">
+        <v>12.37157</v>
+      </c>
+      <c r="F101">
+        <v>12.71457</v>
+      </c>
+      <c r="G101">
+        <v>1.27</v>
+      </c>
+      <c r="H101">
+        <v>12.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>12.2</v>
+      </c>
+      <c r="K101">
+        <v>0.08</v>
+      </c>
+      <c r="L101">
+        <v>12.12</v>
+      </c>
+      <c r="M101">
+        <v>0.5810558490000001</v>
+      </c>
+      <c r="N101">
+        <v>11.538944151</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>11.538944151</v>
+      </c>
+      <c r="Q101">
+        <v>11.618944151</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>10.04425889233803</v>
+      </c>
+      <c r="T101">
+        <v>135.6705663379756</v>
+      </c>
+      <c r="U101">
+        <v>0.0457</v>
+      </c>
+      <c r="V101">
+        <v>0</v>
+      </c>
+      <c r="W101">
+        <v>0.0457</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>20.8585801534544</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
